--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4930,6 +4930,34 @@
         <v>661.544</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>519</v>
+      </c>
+      <c r="C163" t="n">
+        <v>495</v>
+      </c>
+      <c r="D163" t="n">
+        <v>528</v>
+      </c>
+      <c r="E163" t="n">
+        <v>525</v>
+      </c>
+      <c r="F163" t="n">
+        <v>523</v>
+      </c>
+      <c r="G163" t="n">
+        <v>718.9299999999999</v>
+      </c>
+      <c r="H163" t="n">
+        <v>675.8440000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4958,6 +4958,34 @@
         <v>675.8440000000001</v>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>693</v>
+      </c>
+      <c r="C164" t="n">
+        <v>610</v>
+      </c>
+      <c r="D164" t="n">
+        <v>693</v>
+      </c>
+      <c r="E164" t="n">
+        <v>670</v>
+      </c>
+      <c r="F164" t="n">
+        <v>690</v>
+      </c>
+      <c r="G164" t="n">
+        <v>753.256</v>
+      </c>
+      <c r="H164" t="n">
+        <v>1212.796</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4961,28 +4961,56 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>655</v>
+      </c>
+      <c r="C164" t="n">
+        <v>600</v>
+      </c>
+      <c r="D164" t="n">
+        <v>673</v>
+      </c>
+      <c r="E164" t="n">
+        <v>599</v>
+      </c>
+      <c r="F164" t="n">
+        <v>640</v>
+      </c>
+      <c r="G164" t="n">
+        <v>743.721</v>
+      </c>
+      <c r="H164" t="n">
+        <v>1304.524</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="B164" t="n">
+      <c r="B165" t="n">
         <v>693</v>
       </c>
-      <c r="C164" t="n">
+      <c r="C165" t="n">
         <v>610</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D165" t="n">
         <v>693</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E165" t="n">
         <v>670</v>
       </c>
-      <c r="F164" t="n">
+      <c r="F165" t="n">
         <v>690</v>
       </c>
-      <c r="G164" t="n">
+      <c r="G165" t="n">
         <v>753.256</v>
       </c>
-      <c r="H164" t="n">
+      <c r="H165" t="n">
         <v>1212.796</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4961,56 +4961,84 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>655</v>
+        <v>628</v>
       </c>
       <c r="C164" t="n">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="D164" t="n">
-        <v>673</v>
+        <v>625</v>
       </c>
       <c r="E164" t="n">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="F164" t="n">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="G164" t="n">
-        <v>743.721</v>
+        <v>734.186</v>
       </c>
       <c r="H164" t="n">
-        <v>1304.524</v>
+        <v>1388.036</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>655</v>
+      </c>
+      <c r="C165" t="n">
+        <v>600</v>
+      </c>
+      <c r="D165" t="n">
+        <v>673</v>
+      </c>
+      <c r="E165" t="n">
+        <v>599</v>
+      </c>
+      <c r="F165" t="n">
+        <v>640</v>
+      </c>
+      <c r="G165" t="n">
+        <v>743.721</v>
+      </c>
+      <c r="H165" t="n">
+        <v>1304.524</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="B165" t="n">
+      <c r="B166" t="n">
         <v>693</v>
       </c>
-      <c r="C165" t="n">
+      <c r="C166" t="n">
         <v>610</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D166" t="n">
         <v>693</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E166" t="n">
         <v>670</v>
       </c>
-      <c r="F165" t="n">
+      <c r="F166" t="n">
         <v>690</v>
       </c>
-      <c r="G165" t="n">
+      <c r="G166" t="n">
         <v>753.256</v>
       </c>
-      <c r="H165" t="n">
+      <c r="H166" t="n">
         <v>1212.796</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4961,84 +4961,112 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>628</v>
+        <v>578</v>
       </c>
       <c r="C164" t="n">
-        <v>585</v>
+        <v>553</v>
       </c>
       <c r="D164" t="n">
-        <v>625</v>
+        <v>584</v>
       </c>
       <c r="E164" t="n">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="F164" t="n">
-        <v>620</v>
+        <v>578</v>
       </c>
       <c r="G164" t="n">
-        <v>734.186</v>
+        <v>724.651</v>
       </c>
       <c r="H164" t="n">
-        <v>1388.036</v>
+        <v>877.136</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>655</v>
+        <v>628</v>
       </c>
       <c r="C165" t="n">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="D165" t="n">
-        <v>673</v>
+        <v>625</v>
       </c>
       <c r="E165" t="n">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="F165" t="n">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="G165" t="n">
-        <v>743.721</v>
+        <v>734.186</v>
       </c>
       <c r="H165" t="n">
-        <v>1304.524</v>
+        <v>1388.036</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>655</v>
+      </c>
+      <c r="C166" t="n">
+        <v>600</v>
+      </c>
+      <c r="D166" t="n">
+        <v>673</v>
+      </c>
+      <c r="E166" t="n">
+        <v>599</v>
+      </c>
+      <c r="F166" t="n">
+        <v>640</v>
+      </c>
+      <c r="G166" t="n">
+        <v>743.721</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1304.524</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="B166" t="n">
+      <c r="B167" t="n">
         <v>693</v>
       </c>
-      <c r="C166" t="n">
+      <c r="C167" t="n">
         <v>610</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D167" t="n">
         <v>693</v>
       </c>
-      <c r="E166" t="n">
+      <c r="E167" t="n">
         <v>670</v>
       </c>
-      <c r="F166" t="n">
+      <c r="F167" t="n">
         <v>690</v>
       </c>
-      <c r="G166" t="n">
+      <c r="G167" t="n">
         <v>753.256</v>
       </c>
-      <c r="H166" t="n">
+      <c r="H167" t="n">
         <v>1212.796</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5070,6 +5070,34 @@
         <v>1212.796</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>825</v>
+      </c>
+      <c r="C168" t="n">
+        <v>655</v>
+      </c>
+      <c r="D168" t="n">
+        <v>810</v>
+      </c>
+      <c r="E168" t="n">
+        <v>695</v>
+      </c>
+      <c r="F168" t="n">
+        <v>825</v>
+      </c>
+      <c r="G168" t="n">
+        <v>867.674</v>
+      </c>
+      <c r="H168" t="n">
+        <v>1109.524</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5098,6 +5098,34 @@
         <v>1109.524</v>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C169" t="n">
+        <v>780</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1038</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1070</v>
+      </c>
+      <c r="G169" t="n">
+        <v>973.5119999999999</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1007.916</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5101,28 +5101,56 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>1050</v>
       </c>
       <c r="C169" t="n">
+        <v>770</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1040</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1035</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1110</v>
+      </c>
+      <c r="G169" t="n">
+        <v>877.2089999999999</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1064.44</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C170" t="n">
         <v>780</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D170" t="n">
         <v>1020</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E170" t="n">
         <v>1038</v>
       </c>
-      <c r="F169" t="n">
+      <c r="F170" t="n">
         <v>1070</v>
       </c>
-      <c r="G169" t="n">
+      <c r="G170" t="n">
         <v>973.5119999999999</v>
       </c>
-      <c r="H169" t="n">
+      <c r="H170" t="n">
         <v>1007.916</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5101,56 +5101,84 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="C169" t="n">
-        <v>770</v>
+        <v>810</v>
       </c>
       <c r="D169" t="n">
-        <v>1040</v>
+        <v>1150</v>
       </c>
       <c r="E169" t="n">
-        <v>1035</v>
+        <v>1150</v>
       </c>
       <c r="F169" t="n">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="G169" t="n">
         <v>877.2089999999999</v>
       </c>
       <c r="H169" t="n">
-        <v>1064.44</v>
+        <v>1356.992</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>1050</v>
       </c>
       <c r="C170" t="n">
+        <v>770</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1040</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1035</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1110</v>
+      </c>
+      <c r="G170" t="n">
+        <v>877.2089999999999</v>
+      </c>
+      <c r="H170" t="n">
+        <v>1064.44</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C171" t="n">
         <v>780</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D171" t="n">
         <v>1020</v>
       </c>
-      <c r="E170" t="n">
+      <c r="E171" t="n">
         <v>1038</v>
       </c>
-      <c r="F170" t="n">
+      <c r="F171" t="n">
         <v>1070</v>
       </c>
-      <c r="G170" t="n">
+      <c r="G171" t="n">
         <v>973.5119999999999</v>
       </c>
-      <c r="H170" t="n">
+      <c r="H171" t="n">
         <v>1007.916</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5182,6 +5182,34 @@
         <v>1007.916</v>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1133</v>
+      </c>
+      <c r="C172" t="n">
+        <v>800</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1065</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1169</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1077.442</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1056.744</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5185,28 +5185,56 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1138</v>
+      </c>
+      <c r="C172" t="n">
+        <v>785</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1111</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1090</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1125</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1048.837</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1057.004</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="B172" t="n">
+      <c r="B173" t="n">
         <v>1133</v>
       </c>
-      <c r="C172" t="n">
+      <c r="C173" t="n">
         <v>800</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D173" t="n">
         <v>1065</v>
       </c>
-      <c r="E172" t="n">
+      <c r="E173" t="n">
         <v>1169</v>
       </c>
-      <c r="F172" t="n">
+      <c r="F173" t="n">
         <v>1060</v>
       </c>
-      <c r="G172" t="n">
+      <c r="G173" t="n">
         <v>1077.442</v>
       </c>
-      <c r="H172" t="n">
+      <c r="H173" t="n">
         <v>1056.744</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5238,6 +5238,34 @@
         <v>1056.744</v>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>990</v>
+      </c>
+      <c r="C174" t="n">
+        <v>805</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1055</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1077.442</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1062.724</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5241,28 +5241,56 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="C174" t="n">
-        <v>805</v>
+        <v>775</v>
       </c>
       <c r="D174" t="n">
         <v>1030</v>
       </c>
       <c r="E174" t="n">
-        <v>1055</v>
+        <v>1115</v>
       </c>
       <c r="F174" t="n">
-        <v>1015</v>
+        <v>1030</v>
       </c>
       <c r="G174" t="n">
         <v>1077.442</v>
       </c>
       <c r="H174" t="n">
+        <v>1115.816</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>990</v>
+      </c>
+      <c r="C175" t="n">
+        <v>805</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1055</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1077.442</v>
+      </c>
+      <c r="H175" t="n">
         <v>1062.724</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5241,56 +5241,84 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="C174" t="n">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="D174" t="n">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="E174" t="n">
-        <v>1115</v>
+        <v>1168</v>
       </c>
       <c r="F174" t="n">
-        <v>1030</v>
+        <v>1060</v>
       </c>
       <c r="G174" t="n">
         <v>1077.442</v>
       </c>
       <c r="H174" t="n">
-        <v>1115.816</v>
+        <v>1096.628</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="C175" t="n">
-        <v>805</v>
+        <v>775</v>
       </c>
       <c r="D175" t="n">
         <v>1030</v>
       </c>
       <c r="E175" t="n">
-        <v>1055</v>
+        <v>1115</v>
       </c>
       <c r="F175" t="n">
-        <v>1015</v>
+        <v>1030</v>
       </c>
       <c r="G175" t="n">
         <v>1077.442</v>
       </c>
       <c r="H175" t="n">
+        <v>1115.816</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>990</v>
+      </c>
+      <c r="C176" t="n">
+        <v>805</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1055</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1077.442</v>
+      </c>
+      <c r="H176" t="n">
         <v>1062.724</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5322,6 +5322,34 @@
         <v>1062.724</v>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C177" t="n">
+        <v>840</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1097</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1105</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1153.721</v>
+      </c>
+      <c r="H177" t="n">
+        <v>1378.624</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5350,6 +5350,34 @@
         <v>1378.624</v>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>957</v>
+      </c>
+      <c r="C178" t="n">
+        <v>830</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1163.256</v>
+      </c>
+      <c r="H178" t="n">
+        <v>1239.264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5378,6 +5378,34 @@
         <v>1239.264</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>812</v>
+      </c>
+      <c r="C179" t="n">
+        <v>730</v>
+      </c>
+      <c r="D179" t="n">
+        <v>905</v>
+      </c>
+      <c r="E179" t="n">
+        <v>850</v>
+      </c>
+      <c r="F179" t="n">
+        <v>845</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1249.07</v>
+      </c>
+      <c r="H179" t="n">
+        <v>1095.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5381,28 +5381,56 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="C179" t="n">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D179" t="n">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="E179" t="n">
         <v>850</v>
       </c>
       <c r="F179" t="n">
+        <v>820</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1230</v>
+      </c>
+      <c r="H179" t="n">
+        <v>1015.144</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>812</v>
+      </c>
+      <c r="C180" t="n">
+        <v>730</v>
+      </c>
+      <c r="D180" t="n">
+        <v>905</v>
+      </c>
+      <c r="E180" t="n">
+        <v>850</v>
+      </c>
+      <c r="F180" t="n">
         <v>845</v>
       </c>
-      <c r="G179" t="n">
+      <c r="G180" t="n">
         <v>1249.07</v>
       </c>
-      <c r="H179" t="n">
+      <c r="H180" t="n">
         <v>1095.9</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5381,56 +5381,84 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>805</v>
+        <v>866</v>
       </c>
       <c r="C179" t="n">
-        <v>735</v>
+        <v>760</v>
       </c>
       <c r="D179" t="n">
+        <v>950</v>
+      </c>
+      <c r="E179" t="n">
+        <v>930</v>
+      </c>
+      <c r="F179" t="n">
         <v>880</v>
       </c>
-      <c r="E179" t="n">
-        <v>850</v>
-      </c>
-      <c r="F179" t="n">
-        <v>820</v>
-      </c>
       <c r="G179" t="n">
-        <v>1230</v>
+        <v>1163.256</v>
       </c>
       <c r="H179" t="n">
-        <v>1015.144</v>
+        <v>1143.116</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="C180" t="n">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D180" t="n">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="E180" t="n">
         <v>850</v>
       </c>
       <c r="F180" t="n">
+        <v>820</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1230</v>
+      </c>
+      <c r="H180" t="n">
+        <v>1015.144</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>812</v>
+      </c>
+      <c r="C181" t="n">
+        <v>730</v>
+      </c>
+      <c r="D181" t="n">
+        <v>905</v>
+      </c>
+      <c r="E181" t="n">
+        <v>850</v>
+      </c>
+      <c r="F181" t="n">
         <v>845</v>
       </c>
-      <c r="G180" t="n">
+      <c r="G181" t="n">
         <v>1249.07</v>
       </c>
-      <c r="H180" t="n">
+      <c r="H181" t="n">
         <v>1095.9</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5381,84 +5381,112 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>866</v>
+        <v>975</v>
       </c>
       <c r="C179" t="n">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="D179" t="n">
-        <v>950</v>
+        <v>1025</v>
       </c>
       <c r="E179" t="n">
-        <v>930</v>
+        <v>1020</v>
       </c>
       <c r="F179" t="n">
-        <v>880</v>
+        <v>990</v>
       </c>
       <c r="G179" t="n">
         <v>1163.256</v>
       </c>
       <c r="H179" t="n">
-        <v>1143.116</v>
+        <v>1251.12</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>805</v>
+        <v>866</v>
       </c>
       <c r="C180" t="n">
-        <v>735</v>
+        <v>760</v>
       </c>
       <c r="D180" t="n">
+        <v>950</v>
+      </c>
+      <c r="E180" t="n">
+        <v>930</v>
+      </c>
+      <c r="F180" t="n">
         <v>880</v>
       </c>
-      <c r="E180" t="n">
-        <v>850</v>
-      </c>
-      <c r="F180" t="n">
-        <v>820</v>
-      </c>
       <c r="G180" t="n">
-        <v>1230</v>
+        <v>1163.256</v>
       </c>
       <c r="H180" t="n">
-        <v>1015.144</v>
+        <v>1143.116</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="C181" t="n">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D181" t="n">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="E181" t="n">
         <v>850</v>
       </c>
       <c r="F181" t="n">
+        <v>820</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1230</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1015.144</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>812</v>
+      </c>
+      <c r="C182" t="n">
+        <v>730</v>
+      </c>
+      <c r="D182" t="n">
+        <v>905</v>
+      </c>
+      <c r="E182" t="n">
+        <v>850</v>
+      </c>
+      <c r="F182" t="n">
         <v>845</v>
       </c>
-      <c r="G181" t="n">
+      <c r="G182" t="n">
         <v>1249.07</v>
       </c>
-      <c r="H181" t="n">
+      <c r="H182" t="n">
         <v>1095.9</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5490,6 +5490,34 @@
         <v>1095.9</v>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>855</v>
+      </c>
+      <c r="C183" t="n">
+        <v>760</v>
+      </c>
+      <c r="D183" t="n">
+        <v>895</v>
+      </c>
+      <c r="E183" t="n">
+        <v>855</v>
+      </c>
+      <c r="F183" t="n">
+        <v>860</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1353.953</v>
+      </c>
+      <c r="H183" t="n">
+        <v>1139.424</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,46 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MFSPD00</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MFRDD00</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MFHKD00</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MFSAD00</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>MFZSD00</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>MLBSO00</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>LNBSF00</t>
         </is>
@@ -5516,6 +5504,34 @@
       </c>
       <c r="H183" t="n">
         <v>1139.424</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>858</v>
+      </c>
+      <c r="C184" t="n">
+        <v>690</v>
+      </c>
+      <c r="D184" t="n">
+        <v>870</v>
+      </c>
+      <c r="E184" t="n">
+        <v>870</v>
+      </c>
+      <c r="F184" t="n">
+        <v>838</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1401.628</v>
+      </c>
+      <c r="H184" t="n">
+        <v>1010.516</v>
       </c>
     </row>
   </sheetData>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5509,28 +5509,56 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C184" t="n">
-        <v>690</v>
+        <v>745</v>
       </c>
       <c r="D184" t="n">
-        <v>870</v>
+        <v>899</v>
       </c>
       <c r="E184" t="n">
-        <v>870</v>
+        <v>901</v>
       </c>
       <c r="F184" t="n">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="G184" t="n">
         <v>1401.628</v>
       </c>
       <c r="H184" t="n">
+        <v>1078.948</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>858</v>
+      </c>
+      <c r="C185" t="n">
+        <v>690</v>
+      </c>
+      <c r="D185" t="n">
+        <v>870</v>
+      </c>
+      <c r="E185" t="n">
+        <v>870</v>
+      </c>
+      <c r="F185" t="n">
+        <v>838</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1401.628</v>
+      </c>
+      <c r="H185" t="n">
         <v>1010.516</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5509,56 +5509,84 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="C184" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="D184" t="n">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="E184" t="n">
-        <v>901</v>
+        <v>868</v>
       </c>
       <c r="F184" t="n">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="G184" t="n">
         <v>1401.628</v>
       </c>
       <c r="H184" t="n">
-        <v>1078.948</v>
+        <v>1130.376</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C185" t="n">
-        <v>690</v>
+        <v>745</v>
       </c>
       <c r="D185" t="n">
-        <v>870</v>
+        <v>899</v>
       </c>
       <c r="E185" t="n">
-        <v>870</v>
+        <v>901</v>
       </c>
       <c r="F185" t="n">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="G185" t="n">
         <v>1401.628</v>
       </c>
       <c r="H185" t="n">
+        <v>1078.948</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>858</v>
+      </c>
+      <c r="C186" t="n">
+        <v>690</v>
+      </c>
+      <c r="D186" t="n">
+        <v>870</v>
+      </c>
+      <c r="E186" t="n">
+        <v>870</v>
+      </c>
+      <c r="F186" t="n">
+        <v>838</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1401.628</v>
+      </c>
+      <c r="H186" t="n">
         <v>1010.516</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5590,6 +5590,34 @@
         <v>1010.516</v>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>764</v>
+      </c>
+      <c r="C187" t="n">
+        <v>670</v>
+      </c>
+      <c r="D187" t="n">
+        <v>780</v>
+      </c>
+      <c r="E187" t="n">
+        <v>760</v>
+      </c>
+      <c r="F187" t="n">
+        <v>785</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1420.698</v>
+      </c>
+      <c r="H187" t="n">
+        <v>998.816</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5593,28 +5593,56 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="C187" t="n">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D187" t="n">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="E187" t="n">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="F187" t="n">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="G187" t="n">
         <v>1420.698</v>
       </c>
       <c r="H187" t="n">
+        <v>938.1319999999999</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>764</v>
+      </c>
+      <c r="C188" t="n">
+        <v>670</v>
+      </c>
+      <c r="D188" t="n">
+        <v>780</v>
+      </c>
+      <c r="E188" t="n">
+        <v>760</v>
+      </c>
+      <c r="F188" t="n">
+        <v>785</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1420.698</v>
+      </c>
+      <c r="H188" t="n">
         <v>998.816</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5593,56 +5593,84 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>754</v>
+        <v>867</v>
       </c>
       <c r="C187" t="n">
-        <v>665</v>
+        <v>725</v>
       </c>
       <c r="D187" t="n">
-        <v>790</v>
+        <v>875</v>
       </c>
       <c r="E187" t="n">
-        <v>746</v>
+        <v>862</v>
       </c>
       <c r="F187" t="n">
-        <v>775</v>
+        <v>880</v>
       </c>
       <c r="G187" t="n">
         <v>1420.698</v>
       </c>
       <c r="H187" t="n">
-        <v>938.1319999999999</v>
+        <v>1023.308</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="C188" t="n">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D188" t="n">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="E188" t="n">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="F188" t="n">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="G188" t="n">
         <v>1420.698</v>
       </c>
       <c r="H188" t="n">
+        <v>938.1319999999999</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>764</v>
+      </c>
+      <c r="C189" t="n">
+        <v>670</v>
+      </c>
+      <c r="D189" t="n">
+        <v>780</v>
+      </c>
+      <c r="E189" t="n">
+        <v>760</v>
+      </c>
+      <c r="F189" t="n">
+        <v>785</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1420.698</v>
+      </c>
+      <c r="H189" t="n">
         <v>998.816</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5593,84 +5593,110 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>867</v>
-      </c>
-      <c r="C187" t="n">
-        <v>725</v>
-      </c>
+        <v>878</v>
+      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>875</v>
+        <v>890</v>
       </c>
       <c r="E187" t="n">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="F187" t="n">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="G187" t="n">
         <v>1420.698</v>
       </c>
       <c r="H187" t="n">
-        <v>1023.308</v>
+        <v>1040.312</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>754</v>
+        <v>867</v>
       </c>
       <c r="C188" t="n">
-        <v>665</v>
+        <v>725</v>
       </c>
       <c r="D188" t="n">
-        <v>790</v>
+        <v>875</v>
       </c>
       <c r="E188" t="n">
-        <v>746</v>
+        <v>862</v>
       </c>
       <c r="F188" t="n">
-        <v>775</v>
+        <v>880</v>
       </c>
       <c r="G188" t="n">
         <v>1420.698</v>
       </c>
       <c r="H188" t="n">
-        <v>938.1319999999999</v>
+        <v>1023.308</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="C189" t="n">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D189" t="n">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="E189" t="n">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="F189" t="n">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="G189" t="n">
         <v>1420.698</v>
       </c>
       <c r="H189" t="n">
+        <v>938.1319999999999</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>764</v>
+      </c>
+      <c r="C190" t="n">
+        <v>670</v>
+      </c>
+      <c r="D190" t="n">
+        <v>780</v>
+      </c>
+      <c r="E190" t="n">
+        <v>760</v>
+      </c>
+      <c r="F190" t="n">
+        <v>785</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1420.698</v>
+      </c>
+      <c r="H190" t="n">
         <v>998.816</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5593,110 +5593,138 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>878</v>
-      </c>
-      <c r="C187" t="inlineStr"/>
+        <v>896</v>
+      </c>
+      <c r="C187" t="n">
+        <v>725</v>
+      </c>
       <c r="D187" t="n">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="E187" t="n">
-        <v>865</v>
+        <v>891</v>
       </c>
       <c r="F187" t="n">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="G187" t="n">
         <v>1420.698</v>
       </c>
       <c r="H187" t="n">
-        <v>1040.312</v>
+        <v>1017.068</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>867</v>
-      </c>
-      <c r="C188" t="n">
-        <v>725</v>
-      </c>
+        <v>878</v>
+      </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>875</v>
+        <v>890</v>
       </c>
       <c r="E188" t="n">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="F188" t="n">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="G188" t="n">
         <v>1420.698</v>
       </c>
       <c r="H188" t="n">
-        <v>1023.308</v>
+        <v>1040.312</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>754</v>
+        <v>867</v>
       </c>
       <c r="C189" t="n">
-        <v>665</v>
+        <v>725</v>
       </c>
       <c r="D189" t="n">
-        <v>790</v>
+        <v>875</v>
       </c>
       <c r="E189" t="n">
-        <v>746</v>
+        <v>862</v>
       </c>
       <c r="F189" t="n">
-        <v>775</v>
+        <v>880</v>
       </c>
       <c r="G189" t="n">
         <v>1420.698</v>
       </c>
       <c r="H189" t="n">
-        <v>938.1319999999999</v>
+        <v>1023.308</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="C190" t="n">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D190" t="n">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="E190" t="n">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="F190" t="n">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="G190" t="n">
         <v>1420.698</v>
       </c>
       <c r="H190" t="n">
+        <v>938.1319999999999</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>764</v>
+      </c>
+      <c r="C191" t="n">
+        <v>670</v>
+      </c>
+      <c r="D191" t="n">
+        <v>780</v>
+      </c>
+      <c r="E191" t="n">
+        <v>760</v>
+      </c>
+      <c r="F191" t="n">
+        <v>785</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1420.698</v>
+      </c>
+      <c r="H191" t="n">
         <v>998.816</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5728,6 +5728,34 @@
         <v>998.816</v>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>739</v>
+      </c>
+      <c r="C192" t="n">
+        <v>650</v>
+      </c>
+      <c r="D192" t="n">
+        <v>760</v>
+      </c>
+      <c r="E192" t="n">
+        <v>749</v>
+      </c>
+      <c r="F192" t="n">
+        <v>755</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1401.628</v>
+      </c>
+      <c r="H192" t="n">
+        <v>971.776</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5756,6 +5756,34 @@
         <v>971.776</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>708</v>
+      </c>
+      <c r="C193" t="n">
+        <v>665</v>
+      </c>
+      <c r="D193" t="n">
+        <v>730</v>
+      </c>
+      <c r="E193" t="n">
+        <v>693</v>
+      </c>
+      <c r="F193" t="n">
+        <v>715</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1401.628</v>
+      </c>
+      <c r="H193" t="n">
+        <v>946.192</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5759,28 +5759,56 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="C193" t="n">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="D193" t="n">
-        <v>730</v>
+        <v>746</v>
       </c>
       <c r="E193" t="n">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="F193" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="G193" t="n">
         <v>1401.628</v>
       </c>
       <c r="H193" t="n">
+        <v>929.9160000000001</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>708</v>
+      </c>
+      <c r="C194" t="n">
+        <v>665</v>
+      </c>
+      <c r="D194" t="n">
+        <v>730</v>
+      </c>
+      <c r="E194" t="n">
+        <v>693</v>
+      </c>
+      <c r="F194" t="n">
+        <v>715</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1401.628</v>
+      </c>
+      <c r="H194" t="n">
         <v>946.192</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5759,56 +5759,84 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>715</v>
+        <v>736</v>
       </c>
       <c r="C193" t="n">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="D193" t="n">
-        <v>746</v>
+        <v>771.5</v>
       </c>
       <c r="E193" t="n">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="F193" t="n">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="G193" t="n">
         <v>1401.628</v>
       </c>
       <c r="H193" t="n">
-        <v>929.9160000000001</v>
+        <v>983.3200000000001</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="C194" t="n">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="D194" t="n">
-        <v>730</v>
+        <v>746</v>
       </c>
       <c r="E194" t="n">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="F194" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="G194" t="n">
         <v>1401.628</v>
       </c>
       <c r="H194" t="n">
+        <v>929.9160000000001</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>708</v>
+      </c>
+      <c r="C195" t="n">
+        <v>665</v>
+      </c>
+      <c r="D195" t="n">
+        <v>730</v>
+      </c>
+      <c r="E195" t="n">
+        <v>693</v>
+      </c>
+      <c r="F195" t="n">
+        <v>715</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1401.628</v>
+      </c>
+      <c r="H195" t="n">
         <v>946.192</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5759,84 +5759,112 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>736</v>
+        <v>759</v>
       </c>
       <c r="C193" t="n">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="D193" t="n">
-        <v>771.5</v>
+        <v>780</v>
       </c>
       <c r="E193" t="n">
-        <v>723</v>
+        <v>763</v>
       </c>
       <c r="F193" t="n">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="G193" t="n">
         <v>1401.628</v>
       </c>
       <c r="H193" t="n">
-        <v>983.3200000000001</v>
+        <v>1033.5</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>715</v>
+        <v>736</v>
       </c>
       <c r="C194" t="n">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="D194" t="n">
-        <v>746</v>
+        <v>771.5</v>
       </c>
       <c r="E194" t="n">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="F194" t="n">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="G194" t="n">
         <v>1401.628</v>
       </c>
       <c r="H194" t="n">
-        <v>929.9160000000001</v>
+        <v>983.3200000000001</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="C195" t="n">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="D195" t="n">
-        <v>730</v>
+        <v>746</v>
       </c>
       <c r="E195" t="n">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="F195" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="G195" t="n">
         <v>1401.628</v>
       </c>
       <c r="H195" t="n">
+        <v>929.9160000000001</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>708</v>
+      </c>
+      <c r="C196" t="n">
+        <v>665</v>
+      </c>
+      <c r="D196" t="n">
+        <v>730</v>
+      </c>
+      <c r="E196" t="n">
+        <v>693</v>
+      </c>
+      <c r="F196" t="n">
+        <v>715</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1401.628</v>
+      </c>
+      <c r="H196" t="n">
         <v>946.192</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5868,6 +5868,34 @@
         <v>946.192</v>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>700</v>
+      </c>
+      <c r="C197" t="n">
+        <v>633</v>
+      </c>
+      <c r="D197" t="n">
+        <v>730</v>
+      </c>
+      <c r="E197" t="n">
+        <v>678</v>
+      </c>
+      <c r="F197" t="n">
+        <v>710</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1382.558</v>
+      </c>
+      <c r="H197" t="n">
+        <v>945.152</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H197"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5896,6 +5896,34 @@
         <v>945.152</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>732</v>
+      </c>
+      <c r="C198" t="n">
+        <v>710</v>
+      </c>
+      <c r="D198" t="n">
+        <v>750</v>
+      </c>
+      <c r="E198" t="n">
+        <v>704</v>
+      </c>
+      <c r="F198" t="n">
+        <v>720</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1342.512</v>
+      </c>
+      <c r="H198" t="n">
+        <v>984.204</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5899,28 +5899,56 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>732</v>
+        <v>703</v>
       </c>
       <c r="C198" t="n">
-        <v>710</v>
+        <v>674</v>
       </c>
       <c r="D198" t="n">
-        <v>750</v>
+        <v>705</v>
       </c>
       <c r="E198" t="n">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="F198" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="G198" t="n">
         <v>1342.512</v>
       </c>
       <c r="H198" t="n">
+        <v>937.144</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>732</v>
+      </c>
+      <c r="C199" t="n">
+        <v>710</v>
+      </c>
+      <c r="D199" t="n">
+        <v>750</v>
+      </c>
+      <c r="E199" t="n">
+        <v>704</v>
+      </c>
+      <c r="F199" t="n">
+        <v>720</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1342.512</v>
+      </c>
+      <c r="H199" t="n">
         <v>984.204</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5899,56 +5899,84 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>703</v>
+        <v>661</v>
       </c>
       <c r="C198" t="n">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D198" t="n">
-        <v>705</v>
+        <v>683</v>
       </c>
       <c r="E198" t="n">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="F198" t="n">
-        <v>700</v>
+        <v>665</v>
       </c>
       <c r="G198" t="n">
-        <v>1342.512</v>
+        <v>1373.023</v>
       </c>
       <c r="H198" t="n">
-        <v>937.144</v>
+        <v>884.26</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>732</v>
+        <v>703</v>
       </c>
       <c r="C199" t="n">
-        <v>710</v>
+        <v>674</v>
       </c>
       <c r="D199" t="n">
-        <v>750</v>
+        <v>705</v>
       </c>
       <c r="E199" t="n">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="F199" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="G199" t="n">
         <v>1342.512</v>
       </c>
       <c r="H199" t="n">
+        <v>937.144</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>732</v>
+      </c>
+      <c r="C200" t="n">
+        <v>710</v>
+      </c>
+      <c r="D200" t="n">
+        <v>750</v>
+      </c>
+      <c r="E200" t="n">
+        <v>704</v>
+      </c>
+      <c r="F200" t="n">
+        <v>720</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1342.512</v>
+      </c>
+      <c r="H200" t="n">
         <v>984.204</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5899,84 +5899,112 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>661</v>
+        <v>678</v>
       </c>
       <c r="C198" t="n">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D198" t="n">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="E198" t="n">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="F198" t="n">
-        <v>665</v>
+        <v>695</v>
       </c>
       <c r="G198" t="n">
         <v>1373.023</v>
       </c>
       <c r="H198" t="n">
-        <v>884.26</v>
+        <v>910.312</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>703</v>
+        <v>661</v>
       </c>
       <c r="C199" t="n">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D199" t="n">
-        <v>705</v>
+        <v>683</v>
       </c>
       <c r="E199" t="n">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="F199" t="n">
-        <v>700</v>
+        <v>665</v>
       </c>
       <c r="G199" t="n">
-        <v>1342.512</v>
+        <v>1373.023</v>
       </c>
       <c r="H199" t="n">
-        <v>937.144</v>
+        <v>884.26</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>732</v>
+        <v>703</v>
       </c>
       <c r="C200" t="n">
-        <v>710</v>
+        <v>674</v>
       </c>
       <c r="D200" t="n">
-        <v>750</v>
+        <v>705</v>
       </c>
       <c r="E200" t="n">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="F200" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="G200" t="n">
         <v>1342.512</v>
       </c>
       <c r="H200" t="n">
+        <v>937.144</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>732</v>
+      </c>
+      <c r="C201" t="n">
+        <v>710</v>
+      </c>
+      <c r="D201" t="n">
+        <v>750</v>
+      </c>
+      <c r="E201" t="n">
+        <v>704</v>
+      </c>
+      <c r="F201" t="n">
+        <v>720</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1342.512</v>
+      </c>
+      <c r="H201" t="n">
         <v>984.204</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6008,6 +6008,34 @@
         <v>984.204</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>749</v>
+      </c>
+      <c r="C202" t="n">
+        <v>725</v>
+      </c>
+      <c r="D202" t="n">
+        <v>760</v>
+      </c>
+      <c r="E202" t="n">
+        <v>708</v>
+      </c>
+      <c r="F202" t="n">
+        <v>735</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1361.581</v>
+      </c>
+      <c r="H202" t="n">
+        <v>984.204</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6036,6 +6036,34 @@
         <v>984.204</v>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>771</v>
+      </c>
+      <c r="C203" t="n">
+        <v>795</v>
+      </c>
+      <c r="D203" t="n">
+        <v>790</v>
+      </c>
+      <c r="E203" t="n">
+        <v>777</v>
+      </c>
+      <c r="F203" t="n">
+        <v>765</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1355.86</v>
+      </c>
+      <c r="H203" t="n">
+        <v>973.024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6039,28 +6039,56 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>756</v>
+      </c>
+      <c r="C203" t="n">
+        <v>760</v>
+      </c>
+      <c r="D203" t="n">
+        <v>777</v>
+      </c>
+      <c r="E203" t="n">
+        <v>745</v>
+      </c>
+      <c r="F203" t="n">
+        <v>752</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1361.581</v>
+      </c>
+      <c r="H203" t="n">
+        <v>981.864</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B203" t="n">
+      <c r="B204" t="n">
         <v>771</v>
       </c>
-      <c r="C203" t="n">
+      <c r="C204" t="n">
         <v>795</v>
       </c>
-      <c r="D203" t="n">
+      <c r="D204" t="n">
         <v>790</v>
       </c>
-      <c r="E203" t="n">
+      <c r="E204" t="n">
         <v>777</v>
       </c>
-      <c r="F203" t="n">
+      <c r="F204" t="n">
         <v>765</v>
       </c>
-      <c r="G203" t="n">
+      <c r="G204" t="n">
         <v>1355.86</v>
       </c>
-      <c r="H203" t="n">
+      <c r="H204" t="n">
         <v>973.024</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:H205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6039,56 +6039,84 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="C203" t="n">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="D203" t="n">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="E203" t="n">
+        <v>735</v>
+      </c>
+      <c r="F203" t="n">
         <v>745</v>
-      </c>
-      <c r="F203" t="n">
-        <v>752</v>
       </c>
       <c r="G203" t="n">
         <v>1361.581</v>
       </c>
       <c r="H203" t="n">
-        <v>981.864</v>
+        <v>986.284</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>756</v>
+      </c>
+      <c r="C204" t="n">
+        <v>760</v>
+      </c>
+      <c r="D204" t="n">
+        <v>777</v>
+      </c>
+      <c r="E204" t="n">
+        <v>745</v>
+      </c>
+      <c r="F204" t="n">
+        <v>752</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1361.581</v>
+      </c>
+      <c r="H204" t="n">
+        <v>981.864</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B204" t="n">
+      <c r="B205" t="n">
         <v>771</v>
       </c>
-      <c r="C204" t="n">
+      <c r="C205" t="n">
         <v>795</v>
       </c>
-      <c r="D204" t="n">
+      <c r="D205" t="n">
         <v>790</v>
       </c>
-      <c r="E204" t="n">
+      <c r="E205" t="n">
         <v>777</v>
       </c>
-      <c r="F204" t="n">
+      <c r="F205" t="n">
         <v>765</v>
       </c>
-      <c r="G204" t="n">
+      <c r="G205" t="n">
         <v>1355.86</v>
       </c>
-      <c r="H204" t="n">
+      <c r="H205" t="n">
         <v>973.024</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6120,6 +6120,34 @@
         <v>973.024</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>804</v>
+      </c>
+      <c r="C206" t="n">
+        <v>820</v>
+      </c>
+      <c r="D206" t="n">
+        <v>837</v>
+      </c>
+      <c r="E206" t="n">
+        <v>792</v>
+      </c>
+      <c r="F206" t="n">
+        <v>796</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1344.419</v>
+      </c>
+      <c r="H206" t="n">
+        <v>1045.668</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6148,6 +6148,24 @@
         <v>1045.668</v>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="n">
+        <v>790</v>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="n">
+        <v>750</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H207"/>
+  <dimension ref="A1:H208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6166,6 +6166,32 @@
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
     </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>807</v>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="n">
+        <v>906.75</v>
+      </c>
+      <c r="E208" t="n">
+        <v>797</v>
+      </c>
+      <c r="F208" t="n">
+        <v>793</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1348.233</v>
+      </c>
+      <c r="H208" t="n">
+        <v>1007.968</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H208"/>
+  <dimension ref="A1:H209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6192,6 +6192,34 @@
         <v>1007.968</v>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>821</v>
+      </c>
+      <c r="C209" t="n">
+        <v>785</v>
+      </c>
+      <c r="D209" t="n">
+        <v>895</v>
+      </c>
+      <c r="E209" t="n">
+        <v>810</v>
+      </c>
+      <c r="F209" t="n">
+        <v>810</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1348.233</v>
+      </c>
+      <c r="H209" t="n">
+        <v>984.932</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H209"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6195,28 +6195,56 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>821</v>
+        <v>872</v>
       </c>
       <c r="C209" t="n">
-        <v>785</v>
+        <v>840</v>
       </c>
       <c r="D209" t="n">
-        <v>895</v>
+        <v>935</v>
       </c>
       <c r="E209" t="n">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F209" t="n">
-        <v>810</v>
+        <v>845</v>
       </c>
       <c r="G209" t="n">
         <v>1348.233</v>
       </c>
       <c r="H209" t="n">
+        <v>1020.968</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>821</v>
+      </c>
+      <c r="C210" t="n">
+        <v>785</v>
+      </c>
+      <c r="D210" t="n">
+        <v>895</v>
+      </c>
+      <c r="E210" t="n">
+        <v>810</v>
+      </c>
+      <c r="F210" t="n">
+        <v>810</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1348.233</v>
+      </c>
+      <c r="H210" t="n">
         <v>984.932</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6248,6 +6248,34 @@
         <v>984.932</v>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>769</v>
+      </c>
+      <c r="C211" t="n">
+        <v>770</v>
+      </c>
+      <c r="D211" t="n">
+        <v>815</v>
+      </c>
+      <c r="E211" t="n">
+        <v>760</v>
+      </c>
+      <c r="F211" t="n">
+        <v>765</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1338.698</v>
+      </c>
+      <c r="H211" t="n">
+        <v>969.904</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H211"/>
+  <dimension ref="A1:H212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6276,6 +6276,34 @@
         <v>969.904</v>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>774</v>
+      </c>
+      <c r="C212" t="n">
+        <v>805</v>
+      </c>
+      <c r="D212" t="n">
+        <v>785</v>
+      </c>
+      <c r="E212" t="n">
+        <v>759</v>
+      </c>
+      <c r="F212" t="n">
+        <v>761</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1334.884</v>
+      </c>
+      <c r="H212" t="n">
+        <v>969.852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H212"/>
+  <dimension ref="A1:H213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6304,6 +6304,34 @@
         <v>969.852</v>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>826</v>
+      </c>
+      <c r="C213" t="n">
+        <v>765</v>
+      </c>
+      <c r="D213" t="n">
+        <v>855</v>
+      </c>
+      <c r="E213" t="n">
+        <v>805</v>
+      </c>
+      <c r="F213" t="n">
+        <v>797</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1334.884</v>
+      </c>
+      <c r="H213" t="n">
+        <v>1008.748</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H213"/>
+  <dimension ref="A1:H214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6307,28 +6307,56 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="C213" t="n">
-        <v>765</v>
+        <v>792</v>
       </c>
       <c r="D213" t="n">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="E213" t="n">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="F213" t="n">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G213" t="n">
         <v>1334.884</v>
       </c>
       <c r="H213" t="n">
+        <v>1021.852</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>826</v>
+      </c>
+      <c r="C214" t="n">
+        <v>765</v>
+      </c>
+      <c r="D214" t="n">
+        <v>855</v>
+      </c>
+      <c r="E214" t="n">
+        <v>805</v>
+      </c>
+      <c r="F214" t="n">
+        <v>797</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1334.884</v>
+      </c>
+      <c r="H214" t="n">
         <v>1008.748</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H214"/>
+  <dimension ref="A1:H215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6307,56 +6307,84 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>831</v>
+        <v>796</v>
       </c>
       <c r="C213" t="n">
-        <v>792</v>
+        <v>810</v>
       </c>
       <c r="D213" t="n">
-        <v>849</v>
+        <v>815</v>
       </c>
       <c r="E213" t="n">
-        <v>815</v>
+        <v>771</v>
       </c>
       <c r="F213" t="n">
-        <v>798</v>
+        <v>778</v>
       </c>
       <c r="G213" t="n">
         <v>1334.884</v>
       </c>
       <c r="H213" t="n">
-        <v>1021.852</v>
+        <v>982.176</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="C214" t="n">
-        <v>765</v>
+        <v>792</v>
       </c>
       <c r="D214" t="n">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="E214" t="n">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="F214" t="n">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G214" t="n">
         <v>1334.884</v>
       </c>
       <c r="H214" t="n">
+        <v>1021.852</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>826</v>
+      </c>
+      <c r="C215" t="n">
+        <v>765</v>
+      </c>
+      <c r="D215" t="n">
+        <v>855</v>
+      </c>
+      <c r="E215" t="n">
+        <v>805</v>
+      </c>
+      <c r="F215" t="n">
+        <v>797</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1334.884</v>
+      </c>
+      <c r="H215" t="n">
         <v>1008.748</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H215"/>
+  <dimension ref="A1:H216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6388,6 +6388,34 @@
         <v>1008.748</v>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>831</v>
+      </c>
+      <c r="C216" t="n">
+        <v>752</v>
+      </c>
+      <c r="D216" t="n">
+        <v>861</v>
+      </c>
+      <c r="E216" t="n">
+        <v>801</v>
+      </c>
+      <c r="F216" t="n">
+        <v>798</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1334.884</v>
+      </c>
+      <c r="H216" t="n">
+        <v>1019.564</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H216"/>
+  <dimension ref="A1:H217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6416,6 +6416,34 @@
         <v>1019.564</v>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>851</v>
+      </c>
+      <c r="C217" t="n">
+        <v>775</v>
+      </c>
+      <c r="D217" t="n">
+        <v>875</v>
+      </c>
+      <c r="E217" t="n">
+        <v>823</v>
+      </c>
+      <c r="F217" t="n">
+        <v>820</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1334.884</v>
+      </c>
+      <c r="H217" t="n">
+        <v>1043.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H217"/>
+  <dimension ref="A1:H218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6444,6 +6444,34 @@
         <v>1043.38</v>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>808</v>
+      </c>
+      <c r="C218" t="n">
+        <v>745</v>
+      </c>
+      <c r="D218" t="n">
+        <v>875</v>
+      </c>
+      <c r="E218" t="n">
+        <v>859</v>
+      </c>
+      <c r="F218" t="n">
+        <v>798</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1329.163</v>
+      </c>
+      <c r="H218" t="n">
+        <v>1045.356</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H218"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6447,28 +6447,56 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>842</v>
+      </c>
+      <c r="C218" t="n">
+        <v>746</v>
+      </c>
+      <c r="D218" t="n">
+        <v>880</v>
+      </c>
+      <c r="E218" t="n">
+        <v>829</v>
+      </c>
+      <c r="F218" t="n">
+        <v>828</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1334.884</v>
+      </c>
+      <c r="H218" t="n">
+        <v>1100.268</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B218" t="n">
+      <c r="B219" t="n">
         <v>808</v>
       </c>
-      <c r="C218" t="n">
+      <c r="C219" t="n">
         <v>745</v>
       </c>
-      <c r="D218" t="n">
+      <c r="D219" t="n">
         <v>875</v>
       </c>
-      <c r="E218" t="n">
+      <c r="E219" t="n">
         <v>859</v>
       </c>
-      <c r="F218" t="n">
+      <c r="F219" t="n">
         <v>798</v>
       </c>
-      <c r="G218" t="n">
+      <c r="G219" t="n">
         <v>1329.163</v>
       </c>
-      <c r="H218" t="n">
+      <c r="H219" t="n">
         <v>1045.356</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6447,56 +6447,84 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="C218" t="n">
-        <v>746</v>
+        <v>779</v>
       </c>
       <c r="D218" t="n">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E218" t="n">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="F218" t="n">
-        <v>828</v>
+        <v>850</v>
       </c>
       <c r="G218" t="n">
         <v>1334.884</v>
       </c>
       <c r="H218" t="n">
-        <v>1100.268</v>
+        <v>1093.248</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>842</v>
+      </c>
+      <c r="C219" t="n">
+        <v>746</v>
+      </c>
+      <c r="D219" t="n">
+        <v>880</v>
+      </c>
+      <c r="E219" t="n">
+        <v>829</v>
+      </c>
+      <c r="F219" t="n">
+        <v>828</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1334.884</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1100.268</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B219" t="n">
+      <c r="B220" t="n">
         <v>808</v>
       </c>
-      <c r="C219" t="n">
+      <c r="C220" t="n">
         <v>745</v>
       </c>
-      <c r="D219" t="n">
+      <c r="D220" t="n">
         <v>875</v>
       </c>
-      <c r="E219" t="n">
+      <c r="E220" t="n">
         <v>859</v>
       </c>
-      <c r="F219" t="n">
+      <c r="F220" t="n">
         <v>798</v>
       </c>
-      <c r="G219" t="n">
+      <c r="G220" t="n">
         <v>1329.163</v>
       </c>
-      <c r="H219" t="n">
+      <c r="H220" t="n">
         <v>1045.356</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6447,20 +6447,20 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>862</v>
+        <v>875</v>
       </c>
       <c r="C218" t="n">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="D218" t="n">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="E218" t="n">
-        <v>839</v>
+        <v>860</v>
       </c>
       <c r="F218" t="n">
         <v>850</v>
@@ -6469,62 +6469,90 @@
         <v>1334.884</v>
       </c>
       <c r="H218" t="n">
-        <v>1093.248</v>
+        <v>1091.428</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="C219" t="n">
-        <v>746</v>
+        <v>779</v>
       </c>
       <c r="D219" t="n">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E219" t="n">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="F219" t="n">
-        <v>828</v>
+        <v>850</v>
       </c>
       <c r="G219" t="n">
         <v>1334.884</v>
       </c>
       <c r="H219" t="n">
-        <v>1100.268</v>
+        <v>1093.248</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>842</v>
+      </c>
+      <c r="C220" t="n">
+        <v>746</v>
+      </c>
+      <c r="D220" t="n">
+        <v>880</v>
+      </c>
+      <c r="E220" t="n">
+        <v>829</v>
+      </c>
+      <c r="F220" t="n">
+        <v>828</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1334.884</v>
+      </c>
+      <c r="H220" t="n">
+        <v>1100.268</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B220" t="n">
+      <c r="B221" t="n">
         <v>808</v>
       </c>
-      <c r="C220" t="n">
+      <c r="C221" t="n">
         <v>745</v>
       </c>
-      <c r="D220" t="n">
+      <c r="D221" t="n">
         <v>875</v>
       </c>
-      <c r="E220" t="n">
+      <c r="E221" t="n">
         <v>859</v>
       </c>
-      <c r="F220" t="n">
+      <c r="F221" t="n">
         <v>798</v>
       </c>
-      <c r="G220" t="n">
+      <c r="G221" t="n">
         <v>1329.163</v>
       </c>
-      <c r="H220" t="n">
+      <c r="H221" t="n">
         <v>1045.356</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H221"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6556,6 +6556,34 @@
         <v>1045.356</v>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>823</v>
+      </c>
+      <c r="C222" t="n">
+        <v>723</v>
+      </c>
+      <c r="D222" t="n">
+        <v>927.5</v>
+      </c>
+      <c r="E222" t="n">
+        <v>820</v>
+      </c>
+      <c r="F222" t="n">
+        <v>813</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1319.628</v>
+      </c>
+      <c r="H222" t="n">
+        <v>1038.804</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6584,6 +6584,34 @@
         <v>1038.804</v>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>776</v>
+      </c>
+      <c r="C223" t="n">
+        <v>700</v>
+      </c>
+      <c r="D223" t="n">
+        <v>848</v>
+      </c>
+      <c r="E223" t="n">
+        <v>750</v>
+      </c>
+      <c r="F223" t="n">
+        <v>772</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1313.907</v>
+      </c>
+      <c r="H223" t="n">
+        <v>1033.812</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:H224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6587,28 +6587,46 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="n">
+        <v>685</v>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="n">
+        <v>760</v>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="B223" t="n">
+      <c r="B224" t="n">
         <v>776</v>
       </c>
-      <c r="C223" t="n">
+      <c r="C224" t="n">
         <v>700</v>
       </c>
-      <c r="D223" t="n">
+      <c r="D224" t="n">
         <v>848</v>
       </c>
-      <c r="E223" t="n">
+      <c r="E224" t="n">
         <v>750</v>
       </c>
-      <c r="F223" t="n">
+      <c r="F224" t="n">
         <v>772</v>
       </c>
-      <c r="G223" t="n">
+      <c r="G224" t="n">
         <v>1313.907</v>
       </c>
-      <c r="H223" t="n">
+      <c r="H224" t="n">
         <v>1033.812</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H224"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6587,46 +6587,74 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr"/>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>783</v>
+      </c>
       <c r="C223" t="n">
-        <v>685</v>
-      </c>
-      <c r="D223" t="inlineStr"/>
+        <v>700</v>
+      </c>
+      <c r="D223" t="n">
+        <v>856</v>
+      </c>
       <c r="E223" t="n">
-        <v>760</v>
-      </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
+        <v>775</v>
+      </c>
+      <c r="F223" t="n">
+        <v>783</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1319.628</v>
+      </c>
+      <c r="H223" t="n">
+        <v>1020.292</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="n">
+        <v>685</v>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="n">
+        <v>760</v>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="B224" t="n">
+      <c r="B225" t="n">
         <v>776</v>
       </c>
-      <c r="C224" t="n">
+      <c r="C225" t="n">
         <v>700</v>
       </c>
-      <c r="D224" t="n">
+      <c r="D225" t="n">
         <v>848</v>
       </c>
-      <c r="E224" t="n">
+      <c r="E225" t="n">
         <v>750</v>
       </c>
-      <c r="F224" t="n">
+      <c r="F225" t="n">
         <v>772</v>
       </c>
-      <c r="G224" t="n">
+      <c r="G225" t="n">
         <v>1313.907</v>
       </c>
-      <c r="H224" t="n">
+      <c r="H225" t="n">
         <v>1033.812</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6658,6 +6658,34 @@
         <v>1033.812</v>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>767</v>
+      </c>
+      <c r="C226" t="n">
+        <v>700</v>
+      </c>
+      <c r="D226" t="n">
+        <v>838</v>
+      </c>
+      <c r="E226" t="n">
+        <v>749</v>
+      </c>
+      <c r="F226" t="n">
+        <v>758</v>
+      </c>
+      <c r="G226" t="n">
+        <v>1298.651</v>
+      </c>
+      <c r="H226" t="n">
+        <v>1031.576</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H226"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6686,6 +6686,34 @@
         <v>1031.576</v>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>782</v>
+      </c>
+      <c r="C227" t="n">
+        <v>688</v>
+      </c>
+      <c r="D227" t="n">
+        <v>845</v>
+      </c>
+      <c r="E227" t="n">
+        <v>774</v>
+      </c>
+      <c r="F227" t="n">
+        <v>777</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1283.395</v>
+      </c>
+      <c r="H227" t="n">
+        <v>1060.488</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:H228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6689,28 +6689,56 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="C227" t="n">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D227" t="n">
-        <v>845</v>
+        <v>855</v>
       </c>
       <c r="E227" t="n">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="F227" t="n">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="G227" t="n">
         <v>1283.395</v>
       </c>
       <c r="H227" t="n">
+        <v>1066.572</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>782</v>
+      </c>
+      <c r="C228" t="n">
+        <v>688</v>
+      </c>
+      <c r="D228" t="n">
+        <v>845</v>
+      </c>
+      <c r="E228" t="n">
+        <v>774</v>
+      </c>
+      <c r="F228" t="n">
+        <v>777</v>
+      </c>
+      <c r="G228" t="n">
+        <v>1283.395</v>
+      </c>
+      <c r="H228" t="n">
         <v>1060.488</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H228"/>
+  <dimension ref="A1:H229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6689,56 +6689,84 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="C227" t="n">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D227" t="n">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="E227" t="n">
-        <v>781</v>
+        <v>761</v>
       </c>
       <c r="F227" t="n">
-        <v>784</v>
+        <v>767</v>
       </c>
       <c r="G227" t="n">
-        <v>1283.395</v>
+        <v>1291.023</v>
       </c>
       <c r="H227" t="n">
-        <v>1066.572</v>
+        <v>1043.224</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="C228" t="n">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D228" t="n">
-        <v>845</v>
+        <v>855</v>
       </c>
       <c r="E228" t="n">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="F228" t="n">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="G228" t="n">
         <v>1283.395</v>
       </c>
       <c r="H228" t="n">
+        <v>1066.572</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>782</v>
+      </c>
+      <c r="C229" t="n">
+        <v>688</v>
+      </c>
+      <c r="D229" t="n">
+        <v>845</v>
+      </c>
+      <c r="E229" t="n">
+        <v>774</v>
+      </c>
+      <c r="F229" t="n">
+        <v>777</v>
+      </c>
+      <c r="G229" t="n">
+        <v>1283.395</v>
+      </c>
+      <c r="H229" t="n">
         <v>1060.488</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:H230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6689,84 +6689,102 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>776</v>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
-        <v>695</v>
-      </c>
-      <c r="D227" t="n">
-        <v>850</v>
-      </c>
+        <v>725</v>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="n">
-        <v>761</v>
-      </c>
-      <c r="F227" t="n">
-        <v>767</v>
-      </c>
-      <c r="G227" t="n">
-        <v>1291.023</v>
-      </c>
-      <c r="H227" t="n">
-        <v>1043.224</v>
-      </c>
+        <v>758</v>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="C228" t="n">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D228" t="n">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="E228" t="n">
-        <v>781</v>
+        <v>761</v>
       </c>
       <c r="F228" t="n">
-        <v>784</v>
+        <v>767</v>
       </c>
       <c r="G228" t="n">
-        <v>1283.395</v>
+        <v>1291.023</v>
       </c>
       <c r="H228" t="n">
-        <v>1066.572</v>
+        <v>1043.224</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="C229" t="n">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D229" t="n">
-        <v>845</v>
+        <v>855</v>
       </c>
       <c r="E229" t="n">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="F229" t="n">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="G229" t="n">
         <v>1283.395</v>
       </c>
       <c r="H229" t="n">
+        <v>1066.572</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>782</v>
+      </c>
+      <c r="C230" t="n">
+        <v>688</v>
+      </c>
+      <c r="D230" t="n">
+        <v>845</v>
+      </c>
+      <c r="E230" t="n">
+        <v>774</v>
+      </c>
+      <c r="F230" t="n">
+        <v>777</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1283.395</v>
+      </c>
+      <c r="H230" t="n">
         <v>1060.488</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:H231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6788,6 +6788,34 @@
         <v>1060.488</v>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>770</v>
+      </c>
+      <c r="C231" t="n">
+        <v>679</v>
+      </c>
+      <c r="D231" t="n">
+        <v>820</v>
+      </c>
+      <c r="E231" t="n">
+        <v>759</v>
+      </c>
+      <c r="F231" t="n">
+        <v>763</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1271.953</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1064.024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H231"/>
+  <dimension ref="A1:H232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6816,6 +6816,34 @@
         <v>1064.024</v>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>736</v>
+      </c>
+      <c r="C232" t="n">
+        <v>655</v>
+      </c>
+      <c r="D232" t="n">
+        <v>760</v>
+      </c>
+      <c r="E232" t="n">
+        <v>722</v>
+      </c>
+      <c r="F232" t="n">
+        <v>743</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1271.953</v>
+      </c>
+      <c r="H232" t="n">
+        <v>1061.164</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H232"/>
+  <dimension ref="A1:H233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6819,28 +6819,56 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C232" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="D232" t="n">
-        <v>760</v>
+        <v>783</v>
       </c>
       <c r="E232" t="n">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="F232" t="n">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="G232" t="n">
         <v>1271.953</v>
       </c>
       <c r="H232" t="n">
+        <v>1078.636</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>736</v>
+      </c>
+      <c r="C233" t="n">
+        <v>655</v>
+      </c>
+      <c r="D233" t="n">
+        <v>760</v>
+      </c>
+      <c r="E233" t="n">
+        <v>722</v>
+      </c>
+      <c r="F233" t="n">
+        <v>743</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1271.953</v>
+      </c>
+      <c r="H233" t="n">
         <v>1061.164</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H233"/>
+  <dimension ref="A1:H234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6819,56 +6819,84 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>738</v>
+        <v>781</v>
       </c>
       <c r="C232" t="n">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="D232" t="n">
-        <v>783</v>
+        <v>820</v>
       </c>
       <c r="E232" t="n">
-        <v>725</v>
+        <v>770</v>
       </c>
       <c r="F232" t="n">
-        <v>747</v>
+        <v>780</v>
       </c>
       <c r="G232" t="n">
         <v>1271.953</v>
       </c>
       <c r="H232" t="n">
-        <v>1078.636</v>
+        <v>1096.628</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C233" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="D233" t="n">
-        <v>760</v>
+        <v>783</v>
       </c>
       <c r="E233" t="n">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="F233" t="n">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="G233" t="n">
         <v>1271.953</v>
       </c>
       <c r="H233" t="n">
+        <v>1078.636</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>736</v>
+      </c>
+      <c r="C234" t="n">
+        <v>655</v>
+      </c>
+      <c r="D234" t="n">
+        <v>760</v>
+      </c>
+      <c r="E234" t="n">
+        <v>722</v>
+      </c>
+      <c r="F234" t="n">
+        <v>743</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1271.953</v>
+      </c>
+      <c r="H234" t="n">
         <v>1061.164</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H234"/>
+  <dimension ref="A1:H235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6900,6 +6900,34 @@
         <v>1061.164</v>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>745</v>
+      </c>
+      <c r="C235" t="n">
+        <v>650</v>
+      </c>
+      <c r="D235" t="n">
+        <v>770</v>
+      </c>
+      <c r="E235" t="n">
+        <v>730</v>
+      </c>
+      <c r="F235" t="n">
+        <v>750</v>
+      </c>
+      <c r="G235" t="n">
+        <v>1271.953</v>
+      </c>
+      <c r="H235" t="n">
+        <v>1063.348</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H235"/>
+  <dimension ref="A1:H236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6928,6 +6928,34 @@
         <v>1063.348</v>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>704</v>
+      </c>
+      <c r="C236" t="n">
+        <v>625</v>
+      </c>
+      <c r="D236" t="n">
+        <v>759</v>
+      </c>
+      <c r="E236" t="n">
+        <v>690</v>
+      </c>
+      <c r="F236" t="n">
+        <v>702</v>
+      </c>
+      <c r="G236" t="n">
+        <v>1262.419</v>
+      </c>
+      <c r="H236" t="n">
+        <v>1010.984</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H236"/>
+  <dimension ref="A1:H237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6956,6 +6956,34 @@
         <v>1010.984</v>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>665</v>
+      </c>
+      <c r="C237" t="n">
+        <v>575</v>
+      </c>
+      <c r="D237" t="n">
+        <v>658</v>
+      </c>
+      <c r="E237" t="n">
+        <v>619</v>
+      </c>
+      <c r="F237" t="n">
+        <v>660</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1176.605</v>
+      </c>
+      <c r="H237" t="n">
+        <v>902.408</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6959,28 +6959,56 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>650</v>
+      </c>
+      <c r="C237" t="n">
+        <v>576</v>
+      </c>
+      <c r="D237" t="n">
+        <v>660</v>
+      </c>
+      <c r="E237" t="n">
+        <v>620</v>
+      </c>
+      <c r="F237" t="n">
+        <v>641</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1189.953</v>
+      </c>
+      <c r="H237" t="n">
+        <v>921.4400000000001</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="B237" t="n">
+      <c r="B238" t="n">
         <v>665</v>
       </c>
-      <c r="C237" t="n">
+      <c r="C238" t="n">
         <v>575</v>
       </c>
-      <c r="D237" t="n">
+      <c r="D238" t="n">
         <v>658</v>
       </c>
-      <c r="E237" t="n">
+      <c r="E238" t="n">
         <v>619</v>
       </c>
-      <c r="F237" t="n">
+      <c r="F238" t="n">
         <v>660</v>
       </c>
-      <c r="G237" t="n">
+      <c r="G238" t="n">
         <v>1176.605</v>
       </c>
-      <c r="H237" t="n">
+      <c r="H238" t="n">
         <v>902.408</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6959,17 +6959,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C237" t="n">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D237" t="n">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E237" t="n">
         <v>620</v>
@@ -6978,37 +6978,65 @@
         <v>641</v>
       </c>
       <c r="G237" t="n">
-        <v>1189.953</v>
+        <v>1205.209</v>
       </c>
       <c r="H237" t="n">
-        <v>921.4400000000001</v>
+        <v>940.316</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>650</v>
+      </c>
+      <c r="C238" t="n">
+        <v>576</v>
+      </c>
+      <c r="D238" t="n">
+        <v>660</v>
+      </c>
+      <c r="E238" t="n">
+        <v>620</v>
+      </c>
+      <c r="F238" t="n">
+        <v>641</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1189.953</v>
+      </c>
+      <c r="H238" t="n">
+        <v>921.4400000000001</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="B238" t="n">
+      <c r="B239" t="n">
         <v>665</v>
       </c>
-      <c r="C238" t="n">
+      <c r="C239" t="n">
         <v>575</v>
       </c>
-      <c r="D238" t="n">
+      <c r="D239" t="n">
         <v>658</v>
       </c>
-      <c r="E238" t="n">
+      <c r="E239" t="n">
         <v>619</v>
       </c>
-      <c r="F238" t="n">
+      <c r="F239" t="n">
         <v>660</v>
       </c>
-      <c r="G238" t="n">
+      <c r="G239" t="n">
         <v>1176.605</v>
       </c>
-      <c r="H238" t="n">
+      <c r="H239" t="n">
         <v>902.408</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H239"/>
+  <dimension ref="A1:H240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6959,45 +6959,45 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>644</v>
+        <v>668</v>
       </c>
       <c r="C237" t="n">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="D237" t="n">
-        <v>655</v>
+        <v>705</v>
       </c>
       <c r="E237" t="n">
-        <v>620</v>
+        <v>660</v>
       </c>
       <c r="F237" t="n">
-        <v>641</v>
+        <v>670</v>
       </c>
       <c r="G237" t="n">
-        <v>1205.209</v>
+        <v>1214.744</v>
       </c>
       <c r="H237" t="n">
-        <v>940.316</v>
+        <v>979.576</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C238" t="n">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D238" t="n">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E238" t="n">
         <v>620</v>
@@ -7006,37 +7006,65 @@
         <v>641</v>
       </c>
       <c r="G238" t="n">
-        <v>1189.953</v>
+        <v>1205.209</v>
       </c>
       <c r="H238" t="n">
-        <v>921.4400000000001</v>
+        <v>940.316</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>650</v>
+      </c>
+      <c r="C239" t="n">
+        <v>576</v>
+      </c>
+      <c r="D239" t="n">
+        <v>660</v>
+      </c>
+      <c r="E239" t="n">
+        <v>620</v>
+      </c>
+      <c r="F239" t="n">
+        <v>641</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1189.953</v>
+      </c>
+      <c r="H239" t="n">
+        <v>921.4400000000001</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="B239" t="n">
+      <c r="B240" t="n">
         <v>665</v>
       </c>
-      <c r="C239" t="n">
+      <c r="C240" t="n">
         <v>575</v>
       </c>
-      <c r="D239" t="n">
+      <c r="D240" t="n">
         <v>658</v>
       </c>
-      <c r="E239" t="n">
+      <c r="E240" t="n">
         <v>619</v>
       </c>
-      <c r="F239" t="n">
+      <c r="F240" t="n">
         <v>660</v>
       </c>
-      <c r="G239" t="n">
+      <c r="G240" t="n">
         <v>1176.605</v>
       </c>
-      <c r="H239" t="n">
+      <c r="H240" t="n">
         <v>902.408</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H240"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7068,6 +7068,32 @@
         <v>902.408</v>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>720</v>
+      </c>
+      <c r="C241" t="n">
+        <v>592</v>
+      </c>
+      <c r="D241" t="n">
+        <v>683</v>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="n">
+        <v>686</v>
+      </c>
+      <c r="G241" t="n">
+        <v>1176.605</v>
+      </c>
+      <c r="H241" t="n">
+        <v>931.528</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H241"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7094,6 +7094,34 @@
         <v>931.528</v>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>710</v>
+      </c>
+      <c r="C242" t="n">
+        <v>590</v>
+      </c>
+      <c r="D242" t="n">
+        <v>716.25</v>
+      </c>
+      <c r="E242" t="n">
+        <v>627</v>
+      </c>
+      <c r="F242" t="n">
+        <v>645</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1081.256</v>
+      </c>
+      <c r="H242" t="n">
+        <v>903.136</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7097,28 +7097,56 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="C242" t="n">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D242" t="n">
-        <v>716.25</v>
+        <v>669</v>
       </c>
       <c r="E242" t="n">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="F242" t="n">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="G242" t="n">
         <v>1081.256</v>
       </c>
       <c r="H242" t="n">
+        <v>916.292</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>710</v>
+      </c>
+      <c r="C243" t="n">
+        <v>590</v>
+      </c>
+      <c r="D243" t="n">
+        <v>716.25</v>
+      </c>
+      <c r="E243" t="n">
+        <v>627</v>
+      </c>
+      <c r="F243" t="n">
+        <v>645</v>
+      </c>
+      <c r="G243" t="n">
+        <v>1081.256</v>
+      </c>
+      <c r="H243" t="n">
         <v>903.136</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7097,56 +7097,84 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="C242" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D242" t="n">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="E242" t="n">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="F242" t="n">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="G242" t="n">
-        <v>1081.256</v>
+        <v>1109.86</v>
       </c>
       <c r="H242" t="n">
-        <v>916.292</v>
+        <v>926.172</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="C243" t="n">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D243" t="n">
-        <v>716.25</v>
+        <v>669</v>
       </c>
       <c r="E243" t="n">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="F243" t="n">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="G243" t="n">
         <v>1081.256</v>
       </c>
       <c r="H243" t="n">
+        <v>916.292</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>710</v>
+      </c>
+      <c r="C244" t="n">
+        <v>590</v>
+      </c>
+      <c r="D244" t="n">
+        <v>716.25</v>
+      </c>
+      <c r="E244" t="n">
+        <v>627</v>
+      </c>
+      <c r="F244" t="n">
+        <v>645</v>
+      </c>
+      <c r="G244" t="n">
+        <v>1081.256</v>
+      </c>
+      <c r="H244" t="n">
         <v>903.136</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H244"/>
+  <dimension ref="A1:H245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7097,84 +7097,112 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B242" t="n">
         <v>720</v>
       </c>
       <c r="C242" t="n">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D242" t="n">
         <v>665</v>
       </c>
       <c r="E242" t="n">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="F242" t="n">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="G242" t="n">
-        <v>1109.86</v>
+        <v>1157.535</v>
       </c>
       <c r="H242" t="n">
-        <v>926.172</v>
+        <v>955.864</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="C243" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D243" t="n">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="E243" t="n">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="F243" t="n">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="G243" t="n">
-        <v>1081.256</v>
+        <v>1109.86</v>
       </c>
       <c r="H243" t="n">
-        <v>916.292</v>
+        <v>926.172</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="C244" t="n">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D244" t="n">
-        <v>716.25</v>
+        <v>669</v>
       </c>
       <c r="E244" t="n">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="F244" t="n">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="G244" t="n">
         <v>1081.256</v>
       </c>
       <c r="H244" t="n">
+        <v>916.292</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>710</v>
+      </c>
+      <c r="C245" t="n">
+        <v>590</v>
+      </c>
+      <c r="D245" t="n">
+        <v>716.25</v>
+      </c>
+      <c r="E245" t="n">
+        <v>627</v>
+      </c>
+      <c r="F245" t="n">
+        <v>645</v>
+      </c>
+      <c r="G245" t="n">
+        <v>1081.256</v>
+      </c>
+      <c r="H245" t="n">
         <v>903.136</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H245"/>
+  <dimension ref="A1:H246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7206,6 +7206,34 @@
         <v>903.136</v>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>708</v>
+      </c>
+      <c r="C246" t="n">
+        <v>578</v>
+      </c>
+      <c r="D246" t="n">
+        <v>675</v>
+      </c>
+      <c r="E246" t="n">
+        <v>632</v>
+      </c>
+      <c r="F246" t="n">
+        <v>650</v>
+      </c>
+      <c r="G246" t="n">
+        <v>1062.186</v>
+      </c>
+      <c r="H246" t="n">
+        <v>897.884</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H246"/>
+  <dimension ref="A1:H247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7234,6 +7234,34 @@
         <v>897.884</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>675</v>
+      </c>
+      <c r="C247" t="n">
+        <v>570</v>
+      </c>
+      <c r="D247" t="n">
+        <v>680</v>
+      </c>
+      <c r="E247" t="n">
+        <v>607</v>
+      </c>
+      <c r="F247" t="n">
+        <v>645</v>
+      </c>
+      <c r="G247" t="n">
+        <v>993.535</v>
+      </c>
+      <c r="H247" t="n">
+        <v>968.292</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H247"/>
+  <dimension ref="A1:H248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7237,28 +7237,56 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>700</v>
+      </c>
+      <c r="C247" t="n">
+        <v>580</v>
+      </c>
+      <c r="D247" t="n">
+        <v>666</v>
+      </c>
+      <c r="E247" t="n">
+        <v>615</v>
+      </c>
+      <c r="F247" t="n">
+        <v>652</v>
+      </c>
+      <c r="G247" t="n">
+        <v>1004.977</v>
+      </c>
+      <c r="H247" t="n">
+        <v>974.116</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B247" t="n">
+      <c r="B248" t="n">
         <v>675</v>
       </c>
-      <c r="C247" t="n">
+      <c r="C248" t="n">
         <v>570</v>
       </c>
-      <c r="D247" t="n">
+      <c r="D248" t="n">
         <v>680</v>
       </c>
-      <c r="E247" t="n">
+      <c r="E248" t="n">
         <v>607</v>
       </c>
-      <c r="F247" t="n">
+      <c r="F248" t="n">
         <v>645</v>
       </c>
-      <c r="G247" t="n">
+      <c r="G248" t="n">
         <v>993.535</v>
       </c>
-      <c r="H247" t="n">
+      <c r="H248" t="n">
         <v>968.292</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H248"/>
+  <dimension ref="A1:H249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7237,56 +7237,84 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="C247" t="n">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="D247" t="n">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="E247" t="n">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="F247" t="n">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="G247" t="n">
-        <v>1004.977</v>
+        <v>1033.581</v>
       </c>
       <c r="H247" t="n">
-        <v>974.116</v>
+        <v>962.052</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>700</v>
+      </c>
+      <c r="C248" t="n">
+        <v>580</v>
+      </c>
+      <c r="D248" t="n">
+        <v>666</v>
+      </c>
+      <c r="E248" t="n">
+        <v>615</v>
+      </c>
+      <c r="F248" t="n">
+        <v>652</v>
+      </c>
+      <c r="G248" t="n">
+        <v>1004.977</v>
+      </c>
+      <c r="H248" t="n">
+        <v>974.116</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B248" t="n">
+      <c r="B249" t="n">
         <v>675</v>
       </c>
-      <c r="C248" t="n">
+      <c r="C249" t="n">
         <v>570</v>
       </c>
-      <c r="D248" t="n">
+      <c r="D249" t="n">
         <v>680</v>
       </c>
-      <c r="E248" t="n">
+      <c r="E249" t="n">
         <v>607</v>
       </c>
-      <c r="F248" t="n">
+      <c r="F249" t="n">
         <v>645</v>
       </c>
-      <c r="G248" t="n">
+      <c r="G249" t="n">
         <v>993.535</v>
       </c>
-      <c r="H248" t="n">
+      <c r="H249" t="n">
         <v>968.292</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7237,84 +7237,112 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="C247" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D247" t="n">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="E247" t="n">
         <v>643</v>
       </c>
       <c r="F247" t="n">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="G247" t="n">
-        <v>1033.581</v>
+        <v>1062.186</v>
       </c>
       <c r="H247" t="n">
-        <v>962.052</v>
+        <v>936.4160000000001</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="C248" t="n">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="D248" t="n">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="E248" t="n">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="F248" t="n">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="G248" t="n">
-        <v>1004.977</v>
+        <v>1033.581</v>
       </c>
       <c r="H248" t="n">
-        <v>974.116</v>
+        <v>962.052</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>700</v>
+      </c>
+      <c r="C249" t="n">
+        <v>580</v>
+      </c>
+      <c r="D249" t="n">
+        <v>666</v>
+      </c>
+      <c r="E249" t="n">
+        <v>615</v>
+      </c>
+      <c r="F249" t="n">
+        <v>652</v>
+      </c>
+      <c r="G249" t="n">
+        <v>1004.977</v>
+      </c>
+      <c r="H249" t="n">
+        <v>974.116</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B249" t="n">
+      <c r="B250" t="n">
         <v>675</v>
       </c>
-      <c r="C249" t="n">
+      <c r="C250" t="n">
         <v>570</v>
       </c>
-      <c r="D249" t="n">
+      <c r="D250" t="n">
         <v>680</v>
       </c>
-      <c r="E249" t="n">
+      <c r="E250" t="n">
         <v>607</v>
       </c>
-      <c r="F249" t="n">
+      <c r="F250" t="n">
         <v>645</v>
       </c>
-      <c r="G249" t="n">
+      <c r="G250" t="n">
         <v>993.535</v>
       </c>
-      <c r="H249" t="n">
+      <c r="H250" t="n">
         <v>968.292</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H250"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7346,6 +7346,32 @@
         <v>968.292</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>660</v>
+      </c>
+      <c r="C251" t="n">
+        <v>572</v>
+      </c>
+      <c r="D251" t="n">
+        <v>678</v>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="n">
+        <v>645</v>
+      </c>
+      <c r="G251" t="n">
+        <v>955.395</v>
+      </c>
+      <c r="H251" t="n">
+        <v>952.796</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7372,6 +7372,34 @@
         <v>952.796</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>678</v>
+      </c>
+      <c r="C252" t="n">
+        <v>603</v>
+      </c>
+      <c r="D252" t="n">
+        <v>698</v>
+      </c>
+      <c r="E252" t="n">
+        <v>661</v>
+      </c>
+      <c r="F252" t="n">
+        <v>666</v>
+      </c>
+      <c r="G252" t="n">
+        <v>938.2329999999999</v>
+      </c>
+      <c r="H252" t="n">
+        <v>1012.752</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7375,28 +7375,56 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="C252" t="n">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D252" t="n">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="E252" t="n">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="F252" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="G252" t="n">
         <v>938.2329999999999</v>
       </c>
       <c r="H252" t="n">
+        <v>1038.076</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>678</v>
+      </c>
+      <c r="C253" t="n">
+        <v>603</v>
+      </c>
+      <c r="D253" t="n">
+        <v>698</v>
+      </c>
+      <c r="E253" t="n">
+        <v>661</v>
+      </c>
+      <c r="F253" t="n">
+        <v>666</v>
+      </c>
+      <c r="G253" t="n">
+        <v>938.2329999999999</v>
+      </c>
+      <c r="H253" t="n">
         <v>1012.752</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7375,56 +7375,84 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>670</v>
+        <v>645</v>
       </c>
       <c r="C252" t="n">
-        <v>605</v>
+        <v>568</v>
       </c>
       <c r="D252" t="n">
-        <v>685</v>
+        <v>665</v>
       </c>
       <c r="E252" t="n">
-        <v>643</v>
+        <v>604</v>
       </c>
       <c r="F252" t="n">
-        <v>660</v>
+        <v>635</v>
       </c>
       <c r="G252" t="n">
-        <v>938.2329999999999</v>
+        <v>955.395</v>
       </c>
       <c r="H252" t="n">
-        <v>1038.076</v>
+        <v>993.304</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="C253" t="n">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D253" t="n">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="E253" t="n">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="F253" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="G253" t="n">
         <v>938.2329999999999</v>
       </c>
       <c r="H253" t="n">
+        <v>1038.076</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>678</v>
+      </c>
+      <c r="C254" t="n">
+        <v>603</v>
+      </c>
+      <c r="D254" t="n">
+        <v>698</v>
+      </c>
+      <c r="E254" t="n">
+        <v>661</v>
+      </c>
+      <c r="F254" t="n">
+        <v>666</v>
+      </c>
+      <c r="G254" t="n">
+        <v>938.2329999999999</v>
+      </c>
+      <c r="H254" t="n">
         <v>1012.752</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7375,20 +7375,20 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C252" t="n">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="D252" t="n">
         <v>665</v>
       </c>
       <c r="E252" t="n">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="F252" t="n">
         <v>635</v>
@@ -7397,62 +7397,90 @@
         <v>955.395</v>
       </c>
       <c r="H252" t="n">
-        <v>993.304</v>
+        <v>956.956</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>670</v>
+        <v>645</v>
       </c>
       <c r="C253" t="n">
-        <v>605</v>
+        <v>568</v>
       </c>
       <c r="D253" t="n">
-        <v>685</v>
+        <v>665</v>
       </c>
       <c r="E253" t="n">
-        <v>643</v>
+        <v>604</v>
       </c>
       <c r="F253" t="n">
-        <v>660</v>
+        <v>635</v>
       </c>
       <c r="G253" t="n">
-        <v>938.2329999999999</v>
+        <v>955.395</v>
       </c>
       <c r="H253" t="n">
-        <v>1038.076</v>
+        <v>993.304</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="C254" t="n">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D254" t="n">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="E254" t="n">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="F254" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="G254" t="n">
         <v>938.2329999999999</v>
       </c>
       <c r="H254" t="n">
+        <v>1038.076</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>678</v>
+      </c>
+      <c r="C255" t="n">
+        <v>603</v>
+      </c>
+      <c r="D255" t="n">
+        <v>698</v>
+      </c>
+      <c r="E255" t="n">
+        <v>661</v>
+      </c>
+      <c r="F255" t="n">
+        <v>666</v>
+      </c>
+      <c r="G255" t="n">
+        <v>938.2329999999999</v>
+      </c>
+      <c r="H255" t="n">
         <v>1012.752</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H255"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7484,6 +7484,34 @@
         <v>1012.752</v>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>680</v>
+      </c>
+      <c r="C256" t="n">
+        <v>603</v>
+      </c>
+      <c r="D256" t="n">
+        <v>705</v>
+      </c>
+      <c r="E256" t="n">
+        <v>659</v>
+      </c>
+      <c r="F256" t="n">
+        <v>673</v>
+      </c>
+      <c r="G256" t="n">
+        <v>924.884</v>
+      </c>
+      <c r="H256" t="n">
+        <v>1007.084</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H256"/>
+  <dimension ref="A1:H257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7512,6 +7512,34 @@
         <v>1007.084</v>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>785</v>
+      </c>
+      <c r="C257" t="n">
+        <v>674</v>
+      </c>
+      <c r="D257" t="n">
+        <v>772</v>
+      </c>
+      <c r="E257" t="n">
+        <v>749</v>
+      </c>
+      <c r="F257" t="n">
+        <v>752</v>
+      </c>
+      <c r="G257" t="n">
+        <v>930.605</v>
+      </c>
+      <c r="H257" t="n">
+        <v>1117.532</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H257"/>
+  <dimension ref="A1:H258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7515,28 +7515,56 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="C257" t="n">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D257" t="n">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E257" t="n">
         <v>749</v>
       </c>
       <c r="F257" t="n">
+        <v>750</v>
+      </c>
+      <c r="G257" t="n">
+        <v>924.884</v>
+      </c>
+      <c r="H257" t="n">
+        <v>1078.272</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>785</v>
+      </c>
+      <c r="C258" t="n">
+        <v>674</v>
+      </c>
+      <c r="D258" t="n">
+        <v>772</v>
+      </c>
+      <c r="E258" t="n">
+        <v>749</v>
+      </c>
+      <c r="F258" t="n">
         <v>752</v>
       </c>
-      <c r="G257" t="n">
+      <c r="G258" t="n">
         <v>930.605</v>
       </c>
-      <c r="H257" t="n">
+      <c r="H258" t="n">
         <v>1117.532</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H258"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7515,56 +7515,84 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>770</v>
+        <v>700</v>
       </c>
       <c r="C257" t="n">
-        <v>678</v>
+        <v>635</v>
       </c>
       <c r="D257" t="n">
-        <v>770</v>
+        <v>720</v>
       </c>
       <c r="E257" t="n">
-        <v>749</v>
+        <v>705</v>
       </c>
       <c r="F257" t="n">
-        <v>750</v>
+        <v>682</v>
       </c>
       <c r="G257" t="n">
         <v>924.884</v>
       </c>
       <c r="H257" t="n">
-        <v>1078.272</v>
+        <v>1041.352</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="C258" t="n">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D258" t="n">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E258" t="n">
         <v>749</v>
       </c>
       <c r="F258" t="n">
+        <v>750</v>
+      </c>
+      <c r="G258" t="n">
+        <v>924.884</v>
+      </c>
+      <c r="H258" t="n">
+        <v>1078.272</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>785</v>
+      </c>
+      <c r="C259" t="n">
+        <v>674</v>
+      </c>
+      <c r="D259" t="n">
+        <v>772</v>
+      </c>
+      <c r="E259" t="n">
+        <v>749</v>
+      </c>
+      <c r="F259" t="n">
         <v>752</v>
       </c>
-      <c r="G258" t="n">
+      <c r="G259" t="n">
         <v>930.605</v>
       </c>
-      <c r="H258" t="n">
+      <c r="H259" t="n">
         <v>1117.532</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7596,6 +7596,34 @@
         <v>1117.532</v>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>770</v>
+      </c>
+      <c r="C260" t="n">
+        <v>660</v>
+      </c>
+      <c r="D260" t="n">
+        <v>759</v>
+      </c>
+      <c r="E260" t="n">
+        <v>738</v>
+      </c>
+      <c r="F260" t="n">
+        <v>730</v>
+      </c>
+      <c r="G260" t="n">
+        <v>930.605</v>
+      </c>
+      <c r="H260" t="n">
+        <v>1103.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7624,6 +7624,34 @@
         <v>1103.96</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>777</v>
+      </c>
+      <c r="C261" t="n">
+        <v>650</v>
+      </c>
+      <c r="D261" t="n">
+        <v>765</v>
+      </c>
+      <c r="E261" t="n">
+        <v>742</v>
+      </c>
+      <c r="F261" t="n">
+        <v>730</v>
+      </c>
+      <c r="G261" t="n">
+        <v>953.4880000000001</v>
+      </c>
+      <c r="H261" t="n">
+        <v>1146.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H261"/>
+  <dimension ref="A1:H262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7652,6 +7652,34 @@
         <v>1146.08</v>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>877</v>
+      </c>
+      <c r="C262" t="n">
+        <v>699</v>
+      </c>
+      <c r="D262" t="n">
+        <v>834</v>
+      </c>
+      <c r="E262" t="n">
+        <v>853</v>
+      </c>
+      <c r="F262" t="n">
+        <v>796</v>
+      </c>
+      <c r="G262" t="n">
+        <v>987.814</v>
+      </c>
+      <c r="H262" t="n">
+        <v>1230.216</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H262"/>
+  <dimension ref="A1:H263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7655,28 +7655,56 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>875</v>
+      </c>
+      <c r="C262" t="n">
+        <v>697</v>
+      </c>
+      <c r="D262" t="n">
+        <v>832</v>
+      </c>
+      <c r="E262" t="n">
+        <v>843</v>
+      </c>
+      <c r="F262" t="n">
+        <v>795</v>
+      </c>
+      <c r="G262" t="n">
+        <v>978.279</v>
+      </c>
+      <c r="H262" t="n">
+        <v>1216.332</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B262" t="n">
+      <c r="B263" t="n">
         <v>877</v>
       </c>
-      <c r="C262" t="n">
+      <c r="C263" t="n">
         <v>699</v>
       </c>
-      <c r="D262" t="n">
+      <c r="D263" t="n">
         <v>834</v>
       </c>
-      <c r="E262" t="n">
+      <c r="E263" t="n">
         <v>853</v>
       </c>
-      <c r="F262" t="n">
+      <c r="F263" t="n">
         <v>796</v>
       </c>
-      <c r="G262" t="n">
+      <c r="G263" t="n">
         <v>987.814</v>
       </c>
-      <c r="H262" t="n">
+      <c r="H263" t="n">
         <v>1230.216</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H263"/>
+  <dimension ref="A1:H264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7655,56 +7655,84 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>875</v>
+        <v>792</v>
       </c>
       <c r="C262" t="n">
-        <v>697</v>
+        <v>672</v>
       </c>
       <c r="D262" t="n">
-        <v>832</v>
+        <v>792</v>
       </c>
       <c r="E262" t="n">
-        <v>843</v>
+        <v>771</v>
       </c>
       <c r="F262" t="n">
-        <v>795</v>
+        <v>765</v>
       </c>
       <c r="G262" t="n">
-        <v>978.279</v>
+        <v>961.116</v>
       </c>
       <c r="H262" t="n">
-        <v>1216.332</v>
+        <v>1190.904</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>875</v>
+      </c>
+      <c r="C263" t="n">
+        <v>697</v>
+      </c>
+      <c r="D263" t="n">
+        <v>832</v>
+      </c>
+      <c r="E263" t="n">
+        <v>843</v>
+      </c>
+      <c r="F263" t="n">
+        <v>795</v>
+      </c>
+      <c r="G263" t="n">
+        <v>978.279</v>
+      </c>
+      <c r="H263" t="n">
+        <v>1216.332</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B263" t="n">
+      <c r="B264" t="n">
         <v>877</v>
       </c>
-      <c r="C263" t="n">
+      <c r="C264" t="n">
         <v>699</v>
       </c>
-      <c r="D263" t="n">
+      <c r="D264" t="n">
         <v>834</v>
       </c>
-      <c r="E263" t="n">
+      <c r="E264" t="n">
         <v>853</v>
       </c>
-      <c r="F263" t="n">
+      <c r="F264" t="n">
         <v>796</v>
       </c>
-      <c r="G263" t="n">
+      <c r="G264" t="n">
         <v>987.814</v>
       </c>
-      <c r="H263" t="n">
+      <c r="H264" t="n">
         <v>1230.216</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H264"/>
+  <dimension ref="A1:H265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7655,84 +7655,112 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="C262" t="n">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="D262" t="n">
         <v>792</v>
       </c>
       <c r="E262" t="n">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="F262" t="n">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="G262" t="n">
         <v>961.116</v>
       </c>
       <c r="H262" t="n">
-        <v>1190.904</v>
+        <v>1172.86</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>875</v>
+        <v>792</v>
       </c>
       <c r="C263" t="n">
-        <v>697</v>
+        <v>672</v>
       </c>
       <c r="D263" t="n">
-        <v>832</v>
+        <v>792</v>
       </c>
       <c r="E263" t="n">
-        <v>843</v>
+        <v>771</v>
       </c>
       <c r="F263" t="n">
-        <v>795</v>
+        <v>765</v>
       </c>
       <c r="G263" t="n">
-        <v>978.279</v>
+        <v>961.116</v>
       </c>
       <c r="H263" t="n">
-        <v>1216.332</v>
+        <v>1190.904</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>875</v>
+      </c>
+      <c r="C264" t="n">
+        <v>697</v>
+      </c>
+      <c r="D264" t="n">
+        <v>832</v>
+      </c>
+      <c r="E264" t="n">
+        <v>843</v>
+      </c>
+      <c r="F264" t="n">
+        <v>795</v>
+      </c>
+      <c r="G264" t="n">
+        <v>978.279</v>
+      </c>
+      <c r="H264" t="n">
+        <v>1216.332</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B264" t="n">
+      <c r="B265" t="n">
         <v>877</v>
       </c>
-      <c r="C264" t="n">
+      <c r="C265" t="n">
         <v>699</v>
       </c>
-      <c r="D264" t="n">
+      <c r="D265" t="n">
         <v>834</v>
       </c>
-      <c r="E264" t="n">
+      <c r="E265" t="n">
         <v>853</v>
       </c>
-      <c r="F264" t="n">
+      <c r="F265" t="n">
         <v>796</v>
       </c>
-      <c r="G264" t="n">
+      <c r="G265" t="n">
         <v>987.814</v>
       </c>
-      <c r="H264" t="n">
+      <c r="H265" t="n">
         <v>1230.216</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H265"/>
+  <dimension ref="A1:H266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7764,6 +7764,34 @@
         <v>1230.216</v>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>877</v>
+      </c>
+      <c r="C266" t="n">
+        <v>689</v>
+      </c>
+      <c r="D266" t="n">
+        <v>824</v>
+      </c>
+      <c r="E266" t="n">
+        <v>829</v>
+      </c>
+      <c r="F266" t="n">
+        <v>788</v>
+      </c>
+      <c r="G266" t="n">
+        <v>1010.698</v>
+      </c>
+      <c r="H266" t="n">
+        <v>1211.028</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H266"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7792,6 +7792,34 @@
         <v>1211.028</v>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>855</v>
+      </c>
+      <c r="C267" t="n">
+        <v>680</v>
+      </c>
+      <c r="D267" t="n">
+        <v>815</v>
+      </c>
+      <c r="E267" t="n">
+        <v>811</v>
+      </c>
+      <c r="F267" t="n">
+        <v>798</v>
+      </c>
+      <c r="G267" t="n">
+        <v>1004.977</v>
+      </c>
+      <c r="H267" t="n">
+        <v>1199.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H267"/>
+  <dimension ref="A1:H268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7795,28 +7795,56 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>855</v>
+        <v>838</v>
       </c>
       <c r="C267" t="n">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="D267" t="n">
-        <v>815</v>
+        <v>790</v>
       </c>
       <c r="E267" t="n">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="F267" t="n">
-        <v>798</v>
+        <v>767</v>
       </c>
       <c r="G267" t="n">
         <v>1004.977</v>
       </c>
       <c r="H267" t="n">
+        <v>1181.232</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>855</v>
+      </c>
+      <c r="C268" t="n">
+        <v>680</v>
+      </c>
+      <c r="D268" t="n">
+        <v>815</v>
+      </c>
+      <c r="E268" t="n">
+        <v>811</v>
+      </c>
+      <c r="F268" t="n">
+        <v>798</v>
+      </c>
+      <c r="G268" t="n">
+        <v>1004.977</v>
+      </c>
+      <c r="H268" t="n">
         <v>1199.38</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H268"/>
+  <dimension ref="A1:H269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7795,56 +7795,84 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="C267" t="n">
-        <v>667</v>
+        <v>647</v>
       </c>
       <c r="D267" t="n">
-        <v>790</v>
+        <v>765</v>
       </c>
       <c r="E267" t="n">
-        <v>806</v>
+        <v>780</v>
       </c>
       <c r="F267" t="n">
-        <v>767</v>
+        <v>745</v>
       </c>
       <c r="G267" t="n">
         <v>1004.977</v>
       </c>
       <c r="H267" t="n">
-        <v>1181.232</v>
+        <v>1143.74</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>855</v>
+        <v>838</v>
       </c>
       <c r="C268" t="n">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="D268" t="n">
-        <v>815</v>
+        <v>790</v>
       </c>
       <c r="E268" t="n">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="F268" t="n">
-        <v>798</v>
+        <v>767</v>
       </c>
       <c r="G268" t="n">
         <v>1004.977</v>
       </c>
       <c r="H268" t="n">
+        <v>1181.232</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>855</v>
+      </c>
+      <c r="C269" t="n">
+        <v>680</v>
+      </c>
+      <c r="D269" t="n">
+        <v>815</v>
+      </c>
+      <c r="E269" t="n">
+        <v>811</v>
+      </c>
+      <c r="F269" t="n">
+        <v>798</v>
+      </c>
+      <c r="G269" t="n">
+        <v>1004.977</v>
+      </c>
+      <c r="H269" t="n">
         <v>1199.38</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H269"/>
+  <dimension ref="A1:H270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7795,84 +7795,112 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>828</v>
+        <v>845</v>
       </c>
       <c r="C267" t="n">
-        <v>647</v>
+        <v>665</v>
       </c>
       <c r="D267" t="n">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="E267" t="n">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="F267" t="n">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="G267" t="n">
-        <v>1004.977</v>
+        <v>1010.698</v>
       </c>
       <c r="H267" t="n">
-        <v>1143.74</v>
+        <v>1174.732</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="C268" t="n">
-        <v>667</v>
+        <v>647</v>
       </c>
       <c r="D268" t="n">
-        <v>790</v>
+        <v>765</v>
       </c>
       <c r="E268" t="n">
-        <v>806</v>
+        <v>780</v>
       </c>
       <c r="F268" t="n">
-        <v>767</v>
+        <v>745</v>
       </c>
       <c r="G268" t="n">
         <v>1004.977</v>
       </c>
       <c r="H268" t="n">
-        <v>1181.232</v>
+        <v>1143.74</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>855</v>
+        <v>838</v>
       </c>
       <c r="C269" t="n">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="D269" t="n">
-        <v>815</v>
+        <v>790</v>
       </c>
       <c r="E269" t="n">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="F269" t="n">
-        <v>798</v>
+        <v>767</v>
       </c>
       <c r="G269" t="n">
         <v>1004.977</v>
       </c>
       <c r="H269" t="n">
+        <v>1181.232</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>855</v>
+      </c>
+      <c r="C270" t="n">
+        <v>680</v>
+      </c>
+      <c r="D270" t="n">
+        <v>815</v>
+      </c>
+      <c r="E270" t="n">
+        <v>811</v>
+      </c>
+      <c r="F270" t="n">
+        <v>798</v>
+      </c>
+      <c r="G270" t="n">
+        <v>1004.977</v>
+      </c>
+      <c r="H270" t="n">
         <v>1199.38</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H270"/>
+  <dimension ref="A1:H271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7904,6 +7904,34 @@
         <v>1199.38</v>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>855</v>
+      </c>
+      <c r="C271" t="n">
+        <v>680</v>
+      </c>
+      <c r="D271" t="n">
+        <v>818</v>
+      </c>
+      <c r="E271" t="n">
+        <v>832</v>
+      </c>
+      <c r="F271" t="n">
+        <v>794</v>
+      </c>
+      <c r="G271" t="n">
+        <v>1001.163</v>
+      </c>
+      <c r="H271" t="n">
+        <v>1185.964</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H271"/>
+  <dimension ref="A1:H272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7932,6 +7932,34 @@
         <v>1185.964</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>827</v>
+      </c>
+      <c r="C272" t="n">
+        <v>618</v>
+      </c>
+      <c r="D272" t="n">
+        <v>814</v>
+      </c>
+      <c r="E272" t="n">
+        <v>784</v>
+      </c>
+      <c r="F272" t="n">
+        <v>780</v>
+      </c>
+      <c r="G272" t="n">
+        <v>1001.163</v>
+      </c>
+      <c r="H272" t="n">
+        <v>1124.864</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H272"/>
+  <dimension ref="A1:H273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7935,20 +7935,20 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C272" t="n">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D272" t="n">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E272" t="n">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="F272" t="n">
         <v>780</v>
@@ -7957,6 +7957,34 @@
         <v>1001.163</v>
       </c>
       <c r="H272" t="n">
+        <v>1148.836</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>827</v>
+      </c>
+      <c r="C273" t="n">
+        <v>618</v>
+      </c>
+      <c r="D273" t="n">
+        <v>814</v>
+      </c>
+      <c r="E273" t="n">
+        <v>784</v>
+      </c>
+      <c r="F273" t="n">
+        <v>780</v>
+      </c>
+      <c r="G273" t="n">
+        <v>1001.163</v>
+      </c>
+      <c r="H273" t="n">
         <v>1124.864</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H273"/>
+  <dimension ref="A1:H274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7935,48 +7935,48 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>829</v>
+        <v>863</v>
       </c>
       <c r="C272" t="n">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="D272" t="n">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="E272" t="n">
-        <v>793</v>
+        <v>818</v>
       </c>
       <c r="F272" t="n">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="G272" t="n">
         <v>1001.163</v>
       </c>
       <c r="H272" t="n">
-        <v>1148.836</v>
+        <v>1212.38</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C273" t="n">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D273" t="n">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E273" t="n">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="F273" t="n">
         <v>780</v>
@@ -7985,6 +7985,34 @@
         <v>1001.163</v>
       </c>
       <c r="H273" t="n">
+        <v>1148.836</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>827</v>
+      </c>
+      <c r="C274" t="n">
+        <v>618</v>
+      </c>
+      <c r="D274" t="n">
+        <v>814</v>
+      </c>
+      <c r="E274" t="n">
+        <v>784</v>
+      </c>
+      <c r="F274" t="n">
+        <v>780</v>
+      </c>
+      <c r="G274" t="n">
+        <v>1001.163</v>
+      </c>
+      <c r="H274" t="n">
         <v>1124.864</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H274"/>
+  <dimension ref="A1:H275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7935,76 +7935,76 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C272" t="n">
-        <v>640</v>
+        <v>664</v>
       </c>
       <c r="D272" t="n">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="E272" t="n">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="F272" t="n">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="G272" t="n">
         <v>1001.163</v>
       </c>
       <c r="H272" t="n">
-        <v>1212.38</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>829</v>
+        <v>863</v>
       </c>
       <c r="C273" t="n">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="D273" t="n">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="E273" t="n">
-        <v>793</v>
+        <v>818</v>
       </c>
       <c r="F273" t="n">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="G273" t="n">
         <v>1001.163</v>
       </c>
       <c r="H273" t="n">
-        <v>1148.836</v>
+        <v>1212.38</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C274" t="n">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D274" t="n">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E274" t="n">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="F274" t="n">
         <v>780</v>
@@ -8013,6 +8013,34 @@
         <v>1001.163</v>
       </c>
       <c r="H274" t="n">
+        <v>1148.836</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>827</v>
+      </c>
+      <c r="C275" t="n">
+        <v>618</v>
+      </c>
+      <c r="D275" t="n">
+        <v>814</v>
+      </c>
+      <c r="E275" t="n">
+        <v>784</v>
+      </c>
+      <c r="F275" t="n">
+        <v>780</v>
+      </c>
+      <c r="G275" t="n">
+        <v>1001.163</v>
+      </c>
+      <c r="H275" t="n">
         <v>1124.864</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H275"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8044,6 +8044,34 @@
         <v>1124.864</v>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>845</v>
+      </c>
+      <c r="C276" t="n">
+        <v>636</v>
+      </c>
+      <c r="D276" t="n">
+        <v>840</v>
+      </c>
+      <c r="E276" t="n">
+        <v>798</v>
+      </c>
+      <c r="F276" t="n">
+        <v>810</v>
+      </c>
+      <c r="G276" t="n">
+        <v>1001.163</v>
+      </c>
+      <c r="H276" t="n">
+        <v>1193.296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8072,6 +8072,34 @@
         <v>1193.296</v>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>865</v>
+      </c>
+      <c r="C277" t="n">
+        <v>654</v>
+      </c>
+      <c r="D277" t="n">
+        <v>850</v>
+      </c>
+      <c r="E277" t="n">
+        <v>816</v>
+      </c>
+      <c r="F277" t="n">
+        <v>824</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1001.163</v>
+      </c>
+      <c r="H277" t="n">
+        <v>1200.628</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H277"/>
+  <dimension ref="A1:H278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8075,28 +8075,46 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="n">
+        <v>648</v>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="n">
+        <v>818</v>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B277" t="n">
+      <c r="B278" t="n">
         <v>865</v>
       </c>
-      <c r="C277" t="n">
+      <c r="C278" t="n">
         <v>654</v>
       </c>
-      <c r="D277" t="n">
+      <c r="D278" t="n">
         <v>850</v>
       </c>
-      <c r="E277" t="n">
+      <c r="E278" t="n">
         <v>816</v>
       </c>
-      <c r="F277" t="n">
+      <c r="F278" t="n">
         <v>824</v>
       </c>
-      <c r="G277" t="n">
+      <c r="G278" t="n">
         <v>1001.163</v>
       </c>
-      <c r="H277" t="n">
+      <c r="H278" t="n">
         <v>1200.628</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H278"/>
+  <dimension ref="A1:H279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8118,6 +8118,34 @@
         <v>1200.628</v>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>818</v>
+      </c>
+      <c r="C279" t="n">
+        <v>655</v>
+      </c>
+      <c r="D279" t="n">
+        <v>820</v>
+      </c>
+      <c r="E279" t="n">
+        <v>805</v>
+      </c>
+      <c r="F279" t="n">
+        <v>810</v>
+      </c>
+      <c r="G279" t="n">
+        <v>1004.977</v>
+      </c>
+      <c r="H279" t="n">
+        <v>1155.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H279"/>
+  <dimension ref="A1:H280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8146,6 +8146,34 @@
         <v>1155.44</v>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>827</v>
+      </c>
+      <c r="C280" t="n">
+        <v>648</v>
+      </c>
+      <c r="D280" t="n">
+        <v>829</v>
+      </c>
+      <c r="E280" t="n">
+        <v>811</v>
+      </c>
+      <c r="F280" t="n">
+        <v>819</v>
+      </c>
+      <c r="G280" t="n">
+        <v>1035.488</v>
+      </c>
+      <c r="H280" t="n">
+        <v>1198.912</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8121,56 +8121,84 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>818</v>
+        <v>840</v>
       </c>
       <c r="C279" t="n">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="D279" t="n">
-        <v>820</v>
+        <v>838</v>
       </c>
       <c r="E279" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="F279" t="n">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="G279" t="n">
-        <v>1004.977</v>
+        <v>1001.163</v>
       </c>
       <c r="H279" t="n">
-        <v>1155.44</v>
+        <v>1198.756</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>818</v>
+      </c>
+      <c r="C280" t="n">
+        <v>655</v>
+      </c>
+      <c r="D280" t="n">
+        <v>820</v>
+      </c>
+      <c r="E280" t="n">
+        <v>805</v>
+      </c>
+      <c r="F280" t="n">
+        <v>810</v>
+      </c>
+      <c r="G280" t="n">
+        <v>1004.977</v>
+      </c>
+      <c r="H280" t="n">
+        <v>1155.44</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B280" t="n">
+      <c r="B281" t="n">
         <v>827</v>
       </c>
-      <c r="C280" t="n">
+      <c r="C281" t="n">
         <v>648</v>
       </c>
-      <c r="D280" t="n">
+      <c r="D281" t="n">
         <v>829</v>
       </c>
-      <c r="E280" t="n">
+      <c r="E281" t="n">
         <v>811</v>
       </c>
-      <c r="F280" t="n">
+      <c r="F281" t="n">
         <v>819</v>
       </c>
-      <c r="G280" t="n">
+      <c r="G281" t="n">
         <v>1035.488</v>
       </c>
-      <c r="H280" t="n">
+      <c r="H281" t="n">
         <v>1198.912</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H281"/>
+  <dimension ref="A1:H282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8202,6 +8202,34 @@
         <v>1198.912</v>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>832</v>
+      </c>
+      <c r="C282" t="n">
+        <v>662</v>
+      </c>
+      <c r="D282" t="n">
+        <v>820</v>
+      </c>
+      <c r="E282" t="n">
+        <v>815</v>
+      </c>
+      <c r="F282" t="n">
+        <v>817</v>
+      </c>
+      <c r="G282" t="n">
+        <v>1043.593</v>
+      </c>
+      <c r="H282" t="n">
+        <v>1204.788</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8230,6 +8230,34 @@
         <v>1204.788</v>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>835</v>
+      </c>
+      <c r="C283" t="n">
+        <v>664</v>
+      </c>
+      <c r="D283" t="n">
+        <v>824</v>
+      </c>
+      <c r="E283" t="n">
+        <v>817</v>
+      </c>
+      <c r="F283" t="n">
+        <v>810</v>
+      </c>
+      <c r="G283" t="n">
+        <v>1062.663</v>
+      </c>
+      <c r="H283" t="n">
+        <v>1199.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H283"/>
+  <dimension ref="A1:H284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8258,6 +8258,34 @@
         <v>1199.9</v>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>831</v>
+      </c>
+      <c r="C284" t="n">
+        <v>662</v>
+      </c>
+      <c r="D284" t="n">
+        <v>871</v>
+      </c>
+      <c r="E284" t="n">
+        <v>814</v>
+      </c>
+      <c r="F284" t="n">
+        <v>807</v>
+      </c>
+      <c r="G284" t="n">
+        <v>1079.826</v>
+      </c>
+      <c r="H284" t="n">
+        <v>1214.148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H284"/>
+  <dimension ref="A1:H285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8286,6 +8286,34 @@
         <v>1214.148</v>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>835</v>
+      </c>
+      <c r="C285" t="n">
+        <v>665</v>
+      </c>
+      <c r="D285" t="n">
+        <v>835</v>
+      </c>
+      <c r="E285" t="n">
+        <v>816</v>
+      </c>
+      <c r="F285" t="n">
+        <v>815</v>
+      </c>
+      <c r="G285" t="n">
+        <v>1101.279</v>
+      </c>
+      <c r="H285" t="n">
+        <v>1238.692</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
